--- a/kdd/datos_limpios_conKDD.xlsx
+++ b/kdd/datos_limpios_conKDD.xlsx
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>53.69875222816399</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>26.24777183600713</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="4">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>28.5204991087344</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>53.87700534759358</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33.06595365418895</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="7">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.88413547237077</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>53.52049910873441</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="9">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>75.57932263814618</v>
+        <v>75.58</v>
       </c>
     </row>
     <row r="10">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>27.31729055258468</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="11">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>51.42602495543672</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="12">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>44.4295900178253</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>43.31550802139037</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="14">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>27.98573975044564</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="15">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>23.44028520499108</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="16">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>67.8698752228164</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="17">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.88413547237077</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="18">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Para la masa:, 3 tazas de harina, 70 grs de manteca derretida, 1 taza de leche tibia, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, para el pino, 2 a 3 cucharadas de aceite maravilla o canola, 2 cebollas picadas en cuadros, 1/2 kilo de surtido de mariscos, 1 cucharadita de ají color (puede reemplazar por paprika), 1 cucharadita de ají en pasta, 1/2 cucharadita de orégano, sal a gusto</t>
+          <t>para la masa:, 3 tazas de harina, 70 grs de manteca derretida, 1 taza de leche tibia, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, para el pino, 2 a 3 cucharadas de aceite maravilla o canola, 2 cebollas picadas en cuadros, 1/2 kilo de surtido de mariscos, 1 cucharadita de ají color (puede reemplazar por paprika), 1 cucharadita de ají en pasta, 1/2 cucharadita de orégano, sal a gusto</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>48.97504456327985</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="19">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>60.87344028520499</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="20">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29.50089126559715</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="21">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13.99286987522282</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="22">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>50.57932263814617</v>
+        <v>50.58</v>
       </c>
     </row>
     <row r="23">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>42.15686274509804</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="24">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>35.51693404634581</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="25">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>28.5204991087344</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="26">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30.25846702317291</v>
+        <v>30.26</v>
       </c>
     </row>
     <row r="27">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>73.1283422459893</v>
+        <v>73.13</v>
       </c>
     </row>
     <row r="28">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>45.14260249554367</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="29">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>72.9500891265597</v>
+        <v>72.95</v>
       </c>
     </row>
     <row r="30">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>49.68805704099822</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="31">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>54.76827094474153</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="32">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>28.5204991087344</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="33">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>27.80748663101605</v>
+        <v>27.81</v>
       </c>
     </row>
     <row r="34">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>38.14616755793226</v>
+        <v>38.15</v>
       </c>
     </row>
     <row r="35">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>48.97504456327985</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="36">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>37.61140819964349</v>
+        <v>37.61</v>
       </c>
     </row>
     <row r="37">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>25.53475935828877</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="38">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>25.71301247771836</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="39">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>33.06595365418895</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="40">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>28.5204991087344</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="41">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>75.75757575757575</v>
+        <v>75.76000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>41.04278074866311</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="43">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>21.3458110516934</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="44">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>71.21212121212122</v>
+        <v>71.20999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>27.62923351158645</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="47">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>44.4295900178253</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="48">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>43.98395721925134</v>
+        <v>43.98</v>
       </c>
     </row>
     <row r="49">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>51.60427807486632</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="50">
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>9.269162210338679</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="51">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>48.97504456327985</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="52">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>44.96434937611409</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="53">
@@ -2513,11 +2513,7 @@
       <c r="E53" t="n">
         <v>12</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Nan</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>1</v>
@@ -2528,7 +2524,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>39.03743315508022</v>
+        <v>39.04</v>
       </c>
     </row>
     <row r="54">
@@ -2564,7 +2560,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>44.6078431372549</v>
+        <v>44.61</v>
       </c>
     </row>
     <row r="55">
@@ -2604,7 +2600,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>20.63279857397504</v>
+        <v>20.63</v>
       </c>
     </row>
     <row r="56">
@@ -2644,7 +2640,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>21.70231729055259</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="57">
@@ -2684,7 +2680,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>33.06595365418895</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="58">
@@ -2724,7 +2720,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>35.33868092691623</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="59">
@@ -2764,7 +2760,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>30.79322638146167</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="60">
@@ -2804,7 +2800,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>42.15686274509804</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="61">
@@ -2844,7 +2840,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>53.87700534759358</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="62">
@@ -2865,11 +2861,7 @@
       <c r="E62" t="n">
         <v>1</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Nan</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>1</v>
@@ -2880,7 +2872,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>19.42959001782531</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="63">
@@ -2920,7 +2912,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>23.61853832442068</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="64">
@@ -2960,7 +2952,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>37.61140819964349</v>
+        <v>37.61</v>
       </c>
     </row>
     <row r="65">
@@ -3000,7 +2992,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>39.88413547237077</v>
+        <v>39.88</v>
       </c>
     </row>
     <row r="66">
@@ -3040,7 +3032,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>48.97504456327985</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="67">
@@ -3080,7 +3072,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>26.24777183600713</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="68">
@@ -3120,7 +3112,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>28.16399286987522</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="69">
@@ -3160,7 +3152,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>20.81105169340464</v>
+        <v>20.81</v>
       </c>
     </row>
   </sheetData>

--- a/kdd/datos_limpios_conKDD.xlsx
+++ b/kdd/datos_limpios_conKDD.xlsx
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>53.7</v>
+        <v>53.69875222816399</v>
       </c>
     </row>
     <row r="3">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>26.25</v>
+        <v>26.24777183600713</v>
       </c>
     </row>
     <row r="4">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>28.52</v>
+        <v>28.5204991087344</v>
       </c>
     </row>
     <row r="5">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>53.88</v>
+        <v>53.87700534759358</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>33.07</v>
+        <v>33.06595365418895</v>
       </c>
     </row>
     <row r="7">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>39.88</v>
+        <v>39.88413547237077</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>53.52</v>
+        <v>53.52049910873441</v>
       </c>
     </row>
     <row r="9">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>75.58</v>
+        <v>75.57932263814618</v>
       </c>
     </row>
     <row r="10">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>27.32</v>
+        <v>27.31729055258468</v>
       </c>
     </row>
     <row r="11">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>51.43</v>
+        <v>51.42602495543672</v>
       </c>
     </row>
     <row r="12">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>44.43</v>
+        <v>44.4295900178253</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>43.32</v>
+        <v>43.31550802139037</v>
       </c>
     </row>
     <row r="14">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>27.99</v>
+        <v>27.98573975044564</v>
       </c>
     </row>
     <row r="15">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>23.44</v>
+        <v>23.44028520499108</v>
       </c>
     </row>
     <row r="16">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>67.87</v>
+        <v>67.8698752228164</v>
       </c>
     </row>
     <row r="17">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>39.88</v>
+        <v>39.88413547237077</v>
       </c>
     </row>
     <row r="18">
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>48.98</v>
+        <v>48.97504456327985</v>
       </c>
     </row>
     <row r="19">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>60.87</v>
+        <v>60.87344028520499</v>
       </c>
     </row>
     <row r="20">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29.5</v>
+        <v>29.50089126559715</v>
       </c>
     </row>
     <row r="21">
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13.99</v>
+        <v>13.99286987522282</v>
       </c>
     </row>
     <row r="22">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>50.58</v>
+        <v>50.57932263814617</v>
       </c>
     </row>
     <row r="23">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>42.16</v>
+        <v>42.15686274509804</v>
       </c>
     </row>
     <row r="24">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>35.52</v>
+        <v>35.51693404634581</v>
       </c>
     </row>
     <row r="25">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>28.52</v>
+        <v>28.5204991087344</v>
       </c>
     </row>
     <row r="26">
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30.26</v>
+        <v>30.25846702317291</v>
       </c>
     </row>
     <row r="27">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>73.13</v>
+        <v>73.1283422459893</v>
       </c>
     </row>
     <row r="28">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>45.14</v>
+        <v>45.14260249554367</v>
       </c>
     </row>
     <row r="29">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>72.95</v>
+        <v>72.9500891265597</v>
       </c>
     </row>
     <row r="30">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>49.69</v>
+        <v>49.68805704099822</v>
       </c>
     </row>
     <row r="31">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>54.77</v>
+        <v>54.76827094474153</v>
       </c>
     </row>
     <row r="32">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>28.52</v>
+        <v>28.5204991087344</v>
       </c>
     </row>
     <row r="33">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>27.81</v>
+        <v>27.80748663101605</v>
       </c>
     </row>
     <row r="34">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>38.15</v>
+        <v>38.14616755793226</v>
       </c>
     </row>
     <row r="35">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>48.98</v>
+        <v>48.97504456327985</v>
       </c>
     </row>
     <row r="36">
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>37.61</v>
+        <v>37.61140819964349</v>
       </c>
     </row>
     <row r="37">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>25.53</v>
+        <v>25.53475935828877</v>
       </c>
     </row>
     <row r="38">
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>25.71</v>
+        <v>25.71301247771836</v>
       </c>
     </row>
     <row r="39">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>33.07</v>
+        <v>33.06595365418895</v>
       </c>
     </row>
     <row r="40">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>28.52</v>
+        <v>28.5204991087344</v>
       </c>
     </row>
     <row r="41">
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>75.76000000000001</v>
+        <v>75.75757575757575</v>
       </c>
     </row>
     <row r="42">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>41.04</v>
+        <v>41.04278074866311</v>
       </c>
     </row>
     <row r="43">
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>21.35</v>
+        <v>21.3458110516934</v>
       </c>
     </row>
     <row r="44">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>71.20999999999999</v>
+        <v>71.21212121212122</v>
       </c>
     </row>
     <row r="46">
@@ -2252,7 +2252,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>27.63</v>
+        <v>27.62923351158645</v>
       </c>
     </row>
     <row r="47">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>44.43</v>
+        <v>44.4295900178253</v>
       </c>
     </row>
     <row r="48">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>43.98</v>
+        <v>43.98395721925134</v>
       </c>
     </row>
     <row r="49">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>51.6</v>
+        <v>51.60427807486632</v>
       </c>
     </row>
     <row r="50">
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>9.27</v>
+        <v>9.269162210338679</v>
       </c>
     </row>
     <row r="51">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>48.98</v>
+        <v>48.97504456327985</v>
       </c>
     </row>
     <row r="52">
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>44.96</v>
+        <v>44.96434937611409</v>
       </c>
     </row>
     <row r="53">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>39.04</v>
+        <v>39.03743315508022</v>
       </c>
     </row>
     <row r="54">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>44.61</v>
+        <v>44.6078431372549</v>
       </c>
     </row>
     <row r="55">
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>20.63</v>
+        <v>20.63279857397504</v>
       </c>
     </row>
     <row r="56">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>21.7</v>
+        <v>21.70231729055259</v>
       </c>
     </row>
     <row r="57">
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>33.07</v>
+        <v>33.06595365418895</v>
       </c>
     </row>
     <row r="58">
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>35.34</v>
+        <v>35.33868092691623</v>
       </c>
     </row>
     <row r="59">
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>30.79</v>
+        <v>30.79322638146167</v>
       </c>
     </row>
     <row r="60">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>42.16</v>
+        <v>42.15686274509804</v>
       </c>
     </row>
     <row r="61">
@@ -2840,7 +2840,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>53.88</v>
+        <v>53.87700534759358</v>
       </c>
     </row>
     <row r="62">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>19.43</v>
+        <v>19.42959001782531</v>
       </c>
     </row>
     <row r="63">
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>23.62</v>
+        <v>23.61853832442068</v>
       </c>
     </row>
     <row r="64">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>37.61</v>
+        <v>37.61140819964349</v>
       </c>
     </row>
     <row r="65">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>39.88</v>
+        <v>39.88413547237077</v>
       </c>
     </row>
     <row r="66">
@@ -3032,7 +3032,7 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>48.98</v>
+        <v>48.97504456327985</v>
       </c>
     </row>
     <row r="67">
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>26.25</v>
+        <v>26.24777183600713</v>
       </c>
     </row>
     <row r="68">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>28.16</v>
+        <v>28.16399286987522</v>
       </c>
     </row>
     <row r="69">
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>20.81</v>
+        <v>20.81105169340464</v>
       </c>
     </row>
   </sheetData>

--- a/kdd/datos_limpios_conKDD.xlsx
+++ b/kdd/datos_limpios_conKDD.xlsx
@@ -413,51 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>recipe_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>preparation_time</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>min_portion</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>max_portion</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ingredients</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>steps</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ingredient_count</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>duration_level</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>complexity_score</t>
         </is>
@@ -467,39 +472,42 @@
       <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ajiaco chileno</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>40</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>300 grs de carne asada, puede ser más, 2 cucharadas de aceite, 1 cebolla grande o 2 cebollas medianas, 4 papas medianas, 2 ajos, 1 trozo pequeño de pimentón rojo, 1/2 cucharadita de orégano, sal, pimienta a gusto, merkén, ají color, 1 huevo por persona, 2 cucharadas de perejil picado, 1 litro de caldo de carne</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>1-cortamos la carne en tiras y las papas a lo largo (en juliana). reservar., 2-se corta la cebolla en pluma y se coloca en una olla con el aceite, se fríe por unos minutos, luego agregamos el ajo y el pimentón. enseguida añadir la carne y los aliños (sal, pimienta, ají color, orégano, merkén). luego se echan las papas y finalmente agrega el caldo de carne o agua., 3-se cocina por unos 20 minutos., 4-mientras tanto podemos pochar el huevo o simplemente cocinarlo por 10 minutos en agua hervida., 5-se sirve en un plato hondo y se puede optar por colocar el huevo al principio o al final. luego el caldo y resto de ingredientes. se coloca encima perejil picado y merkén (optativo).</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>15</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>53.69875222816399</v>
       </c>
     </row>
@@ -507,39 +515,42 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Alfajores chilenos</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>35</v>
-      </c>
-      <c r="D3" t="n">
-        <v>20</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>1 1/2 taza de harina cernida, 5 yemas, 1 cucharada de coñac o pisco, manjar</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>1-colocar la harina en un bol y añadir las yemas una a una, y luego lentamente el licor. mezclar bien y formar una masa lisa, firme y seca (en el caso de quedar extremadamente seca, añada pequeñas cantidades de agua)., 2-uslerear la masa dejándola muy delgada; corte círculos de 4 a 5 cms., 3-colocar los alfajores en una lata limpia enmantequillada., 4-llevar a horno precalentado a 400°f (200°c) por 8 a 10 min., 5-unir de a dos con el manjar.</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>26.24777183600713</v>
       </c>
     </row>
@@ -547,39 +558,42 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Arroz con leche</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>35</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>1/2 taza de arroz, 2 1/2 tazas de leche líquida, 1 palito de canela, 1/2 taza de azúcar (puede ser menos o más dependiendo del dulzor que desee), canela en polvo para decorar</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1-algunas personas lavan el arroz antes de usarlo, en esta receta no lo hago., 2-colocar el arroz crudo en un olla con 2 tazas de leche y palo de canela. cocinar por unos 25 a 30 minutos, luego agregar el azúcar y cocinar por unos 3 a 5 minutos más. finalmente agregar la media taza de leche fría, revolver bien y apagar. dejar reposar. se puede servir tibio o totalmente frío. decorar con canela en polvo si desea.</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>28.5204991087344</v>
       </c>
     </row>
@@ -587,39 +601,42 @@
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Berlines chilenos</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>45</v>
       </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>1 sobre de levadura en polvo (7grs/ 2 cucharaditas), 1/4 taza de agua tibia (105°-115°f) (40°-46°c), 60 grs de mantequilla sin sal, 1/2 taza de azúcar granulada, 3 yemas, 3 tazas de harina sin polvos de hornear, 1 taza de leche, 1/2 litro de aceite vegetal, azúcar flor (glas) para espolvorear, 1 litro de leche, 1/2 taza de maicena, 1/2 taza de azúcar granulada, 1/2 cucharadita de esencia de vainilla, 5 yemas</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>1-en un pequeño bol colocar un poquito de agua, 1/4 de taza está bien con una pizca de azúcar y mezclar con la levadura. dejar reposar por unos 10 minutos., 2-mientras tanto en otro bol o mezcladora, batir la mantequilla con la media taza de azúcar, luego añadir las 3 yemas de huevo., 3-enseguida agregar la mezcla de levadura, y la harina poco a poco alternando con la leche., 4-formar una bola, tapar y dejar reposar unos 25 a 30 minutos., 5-luego dividir la masa en dos., 6-ir formando bolas del tamaño de un puño de mano. colocar sobre una lata cubierta de papel de mantequilla, en el caso que desee hacerlos en el horno., 7-nuevamente dejar reposar los berlines unos 20 minutos., 8-aplastar un poco y calentar el aceite por unos 5 minutos a fuego medio. cuando el aceite esté listo, bajar el nivel al mínimo y freír 6 minutos por lado., 9-si lo desea hornear debe precalentar el horno a 350°f (180°c) y hornear por unos 18 minutos., 10-una vez listos los berlines, hacerles un corte en el medio, pero solo hasta la mitad y rellenarlos con la crema pastelera. espolvorear con azúcar flor (glas)., 11-primero batir las yemas con un poquito de leche, luegro agregar la maicena y un poco más de leche para poder disolver todo bien. reservar., 12-en una olla colocar el resto de leche y azúcar. y un poco antes que comience a hervir, agregar la vainilla y la mezcla de yemas con maicena, la cual se puede colar antes de agregar. y de ahí a fuego bajo comenzar a revolver constantemente para que no se pegue ni forme grumos, continuar hasta que la crema se espese. dejar hervir un minuto y apagar. enfriar antes de usar.</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>14</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>53.87700534759358</v>
       </c>
     </row>
@@ -627,39 +644,42 @@
       <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Cachitos con manjar</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>35</v>
-      </c>
-      <c r="D6" t="n">
-        <v>30</v>
       </c>
       <c r="E6" t="n">
         <v>30</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>500 gr harina sin polvos, 1 pizca de sal, 8 yemas de huevo, 120 gr de mantequilla blanda, 60 ml de vino blanco, 60 ml agua, 1 cucharadita de esencia de vainilla</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>1-poner la harina en el mesón y formar una corona., 2-colocar en el centro sal, yemas, mantequilla en trozos, vino, agua y vainilla., 3-mezclar todo hasta unir bien y poder comenzar amasar la masa hasta que esté uniforme., 4-formar una bola, envolver en plástico y llevar al refrigerador por 30 minutos., 5-luego dividir en 3 o 2 trozos. y estirar cada trozo de masa con el uslero, dejar la masa delgada, formar un rectángulo., 6-cortar tiras de 20 cm de largo x 2 cm de ancho., 7-enmantequillar los moldes y si no tienen, pueden hacer unos similares con papel de aluminio., 8-envolver cada masa (tira) desde el extremo más delgado al más ancho., 9-llevar al horno precalentado a 180°c (350°f) por 20 minutos., 10-una vez listos, retirar de los moldes y rellenar con manjar.</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>7</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>33.06595365418895</v>
       </c>
     </row>
@@ -667,39 +687,42 @@
       <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Calzones rotos</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>35</v>
       </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
       <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>3 tazas de harina cernida, 1 cucharada polvos de hornear, 3/4 taza de azúcar flor cernida (es el azúcar en polvo), 2 cucharadas de margarina, 1 huevo, 2 yemas, ralladura de 1 limón, 1/2 taza de agua quizás un poco más, aceite para freír, azúcar flor para espolvorear</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>1-unir los ingredientes secos, la harina, los polvos y azúcar. luego la ralladura de limón., 2-enseguida agregar el huevo y después las yemas una a una., 3-incorporar la mantequilla ablandada y unir bien la masa. finalmente agregar agua suficiente para formar una masa homogénea., 4-uslerear la masa y dejarla aproximadamente 1/2 cm de grosor. cortar rectángulos de 10 cm por 5 cm. luego hacer sobre ellos un corte vertical de unos 3 cm y pasar un extremo del rectángulo por este ojal., 5-freír en aceite caliente, deben quedar dorados., 6-escurrirlos bien y dejarlos en papel absorbente., 7-finalmente espolvorear con azúcar flor.</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>39.88413547237077</v>
       </c>
     </row>
@@ -707,39 +730,42 @@
       <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Cazuela de ave</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>35</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2 trutos de pollo, 4 papas medianas, 2 trozos pequeños de zapallo, 1 choclo entero, 1 zanahoria cortada en tiras, 1 trozo pequeño de morron (puede ser verde o rojo), 1 diente de ajo, 1 rama de apio, 1 rama de perejil, 1/2 cebolla, 3/4 taza de surtido de verduritas (porotos verdes y arvejas), sal, pimienta, comino y orégano, perejil a gusto, 4 cucharadas de arroz o 1/2 taza de cabellos de ángel</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>1-no es necesario hacer un sofrito, ya que al cocer todas las verduras y pollo, suelta los sabores naturales., 2-así que en una olla grande colocamos los trozos de pollo sin cuero, luego las papas enteras peladas, trozos de zapallo, el choclo partido en dos, el ajo entero, así también el trozo de cebolla y el resto de verduras, sal, pimienta, comino, orégano a gusto. y las ramas de apio y perejil enteras., 3-se lleva a cocer con agua tibia o fría y al momento que comienza a hervir se le agrega el arroz, éste al soltar su almidón provoca que el caldo se espese por si solo. y esta cocción dura apróximadamente unos 25 minutos a fuego medio se debe ir revolviendo de vez en cuando. si en el caso que aún le falte cocción al arroz y las papas o el zapallo ya estan listos, se retiran estas dos verduras momentáneamente porque se pueden recocer y luego se vuelven a colocar en el caldo., 4-*también pueden usar cabellos de ángel o sémola en reemplazo del arroz.</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>16</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>53.52049910873441</v>
       </c>
     </row>
@@ -747,39 +773,42 @@
       <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>13</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Cazuela de pavo con chuchoca</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>80</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>1 cucharada de aceite, 4 presas de pavo, 1/2 cebolla cortada en dos, 1/2 unidad de pimentón rojo, 2 dientes de ajos pelados, 1 zanahoria pelada y cortada a lo largo, 1/2 cucharita de orégano, 1 cucharadita de ají color (paprika), sal y pímienta a gusto, 4 papas, 4 trozos de zapallo camote, 4 trozos de choclos (maíz) (1 choclo partido en dos o 3), 1 rama de perejil, 1 cucharadita de perejil picado, 3/4 taza de porotos verdes picados, 3 o 4 cucharadas de chuchoca (maíz molido)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>1-lavar las presas de pavo y secarlas muy bien., 2-luego en una olla calentar el aceite y sellar las presas de pavo. retirar., 3-en ese mismo aceite, saltear la cebolla y ajo. este proceso dura 2 minutos., 4-agregar las presas de pavo,pimentón, zanahorias y sazonar con sal, pimienta, ají color, orégano, rama de perejil y añadir 1 1/2 litros de agua caliente aproximadamente., 5-cocinar por unos 20 minutos., 6-reducir el calor y añadir las papas enteras peladas, trozos de zapallo, choclos y cocinar por unos 15 minutos , añadir los porotos verdes y cocinar por unos 3 minutos más., 7-luego a fuego medio/bajo añadir la chuchoca en forma de lluvia, revolver muy bien. cocinar unos 4 minutos más., 8-servir en un plato hondo con un trozo de pavo, 1 papa, 1 trozo de zapallo, 1 trozo de choclo, caldo con verduras e idealmente con perejil picado encima.</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>16</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>75.57932263814618</v>
       </c>
     </row>
@@ -787,39 +816,42 @@
       <c r="A10" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Chacarero, sandwich chileno</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>14</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>1 pan para sandwich, puede usar marraqueta, pan frica también o la receta del blog, 220 grs de carne, puede usar lomo o asiento (carne en láminas delgadas), 4 rodajas de tomate, 1/2 taza de porotos verdes cocidos y cortados a lo largo, 1 cucharada de ají verde picado, 1 cucharada de mayonesa (puede usar mantequilla)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>1-en un sartén con un poquito de aceite o en una plancha, cocinar la carne aliñada con un poco de sal. esta carne se cocina rápido. no más allá de 2 minutos por lado, sino quedará seca., 2-abrir el pan y untar cada tapa con mayonesa o mantequilla., 3-colocar en la base del pan los trozos de carne, enseguida el tomate, porotos verdes y ají picado., 4-cerrar el pan y disfrutar!</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>9</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>27.31729055258468</v>
       </c>
     </row>
@@ -827,39 +859,42 @@
       <c r="A11" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Charquicán de cochayuyo</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>40</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>1 taza de cochayuyo cocido y picado, 4 papas grandes, 2 tazas de zapallo camote, 1 cebolla pequeña picada en cuadros, 1 diente de ajo, 1 trozo de morrón rojo picado, 1 cucharada de aceite, 1 taza de verduritas surtidas cocidas (porotos verdes, zanahorias, arvejas, etc), 1 cucharadita de ají color, ½ cucharadita de orégano, sal y pimienta a gusto</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>1-para el cochayuyo debe dejarlo remojando la noche anterior con agua y una pizca de vinagre. al siguiente día debe cocinarlo en abundante agua por unos 25 a 30 minutos. estilar y cortar en cuadros., 2-en una olla cocer las papas peladas y picadas con el zapallo, agregar un poco de sal y cocinar por unos 15 minutos. retirar el agua en exceso y moler un poco., 3-mientras se cocinan las papas y el zapallo preparar el sofrito con la cucharada de aceite, freír la cebolla y el ajo por unos 4 a 5 minutos. agregar el morrón rojo y sazonar con el ají color, orégano, sal y pimienta. si desea también puede agregar un poco de comino, pero es totalmente opcional. esto toma unos unos 3 minutos. agregar el cochayuyo, mezclar todo muy bien., 4-añadir esta mezcla a las papas y zapallo. agregar las verduritas elegidas. revolver todo muy bien hasta integrar todos los ingredientes., 5-servir acompañado de un huevo frito o pochado.</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>14</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>51.42602495543672</v>
       </c>
     </row>
@@ -867,39 +902,42 @@
       <c r="A12" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="n">
+        <v>19</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Chupe de jaibas</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>35</v>
       </c>
-      <c r="D12" t="n">
-        <v>6</v>
-      </c>
       <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">30 grs de mantequilla, 1 cebolla mediana cortada en cuadros pequeños, 1 ajo picado finamente, sal y pimienta a gusto, 1 taza de vino blanco, 1/2 kilo de carne de jaiba, 350 ml de leche líquida, 50 grs de mantequilla, 50 grs de harina sin polvos de hornear, una pizca de nuez moscada, 200 grs de queso mantecoso, </t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>1-en un sartén freír a fuego lento junto con la mantequilla (30 grs.) la cebolla. apróximadamente unos 8 minutos. luego agregar el ajo picado. agregar sal y pimienta. luego agregar el vino blanco dejar hervir uns minutos para posteriormente añadir la carne de jaiba. hervir a fuego lento hasta que reduzcan los jugos., 2-mientras tanto en una olla preparamos una salsa blanca derritiendo la mantequilla, luego agregar la harina de golpe, batir bien y cuando esta mezcla esté sin grumos se puede agregar la leche poco a poco, aliñar con sal , pimienta y nuez moscada., 3-luego agregamos la salsa blanca a la mezcla de jaiba, unir bien. luego se coloca en pocillos de greda o simplemente en una fuente que pueda ir al horno. colocarle trozos de queso mantecoso. llevar al horno a gratinar por unos 5 minutos., 4-*mi suegro le agregó unos huevos duros, pero esta parte es totalmente optativa.</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>12</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>44.4295900178253</v>
       </c>
     </row>
@@ -907,39 +945,42 @@
       <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Chupe de locos</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>42</v>
       </c>
-      <c r="D13" t="n">
-        <v>6</v>
-      </c>
       <c r="E13" t="n">
         <v>6</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>4 locos grandes o 1 tarro de locos cocidos, 1 pan (puede ser 1 marraqueta o 3 láminas de pan de molde), 3/4 taza de leche líquida, 1 cucharada de aceite, 1 cebolla picada en cuadros, 1 trozo de pimentón rojo picado en cuadros, 3/4 taza de queso rallado, sal y pimienta a gusto, 1 cucharadita de mantequilla, perejil picado (opcional)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>1-si ocupa locos crudos, debe cocinarlos en una olla con agua y sal, por 50 min., 2-una vez listos picarlos en cuadros. si ocupa locos en tarro, estos vienen listos para usar., 3-remojar el pan en la leche por unos 20 minutos. luego pasar por el colador., 4-en un sartén con aceite freír la cebolla picada por unos 4 minutos a fuego medio., 5-luego agregar el pimentón picado y cocinar unos 2 minutos más., 6-agregar los locos picados, pan remojado y un poco del caldo de la cocción o el caldo que viene en el tarro, 1/2 taza app., 7-luego añadir la mitad del queso, mantequilla, sazonar con sal y pimienta a gusto., 8-pasar la mezcla a un molde idealmente de greda o el que tenga., 9-luego poner el resto de queso encima y llevar al horno a gratinar., 10-si gusta pueden servir con perejil picado encima.</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>10</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>43.31550802139037</v>
       </c>
     </row>
@@ -947,39 +988,42 @@
       <c r="A14" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Pan para sandwich</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>12</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>1 taza de agua tibia (105°-115°f) (40°-46°c), 1 sobre de levadura seca en polvo\xa0 (7 grs)(2 1/4 de cucharadita), 1 taza de leche liquida tibia (105°-115°f) (40°-46°c), 2 cucharadas de mantequilla derretida, 2 cucharadas de azúcar granulada, 1 1/2 cucharaditas de sal, 5 1/2 a 6 tazas de harina, 1 yema de huevo con 1 cucharadita de agua</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>1-combinar 1/2 taza de agua tibia con la levadura y una pizca de azúcar granulada en un pequeño bol. revolver hasta disolver bien y dejar reposar unos 10 minutos., 2-en un bol grande colocar el agua restante, leche, mantequilla, azúcar y sal. luego agregar la mezcla de levadura, revolver un poco y agregar 2 tazas de harina y mezclar muy bien., 3-continuar revolviendo (puede ser con la ayuda de una mezcladora o una batidora eléctrica que traiga las piezas para amasar). hasta lograr incorporar bien la harina y lograr una mezcla cremosa, posteriormente ir incorporando de a 1/2 taza de harina., 4-cuando la masa ya no se pegue en el bol, se puede comenzar amasar unos minutos., 5-luego en otro bol engrasado con aceite o mantequilla, colocamos la masa allí en forma de bola y dejamos reposar la masa tapada con papel de plástico o un paño de cocina por una hora o hasta que doble su volumen la masa., 6-una vez listo, formamos los panes, podrían salir unos 8 unidades o más, todo depende del tamaño que deseen sus panes. pueden hacerlos más pequeños para hacer hamburguesas y en ese caso podrían salir hasta 12 unidades., 7-colocar el pan en la bandeja del horno cubierta con papel de mantequilla. dejamos reposar nuevamente el pan., 8-precalentar el horno a 400°f (200°c)., 9-justo antes de colocar el pan en el horno, pincelar cada pan con la mezcla de yema más agua., 10-hornear por unos 15 a 20 minutos.</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>27.98573975044564</v>
       </c>
     </row>
@@ -987,39 +1031,42 @@
       <c r="A15" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="n">
+        <v>23</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Cocadas y confites</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>20</v>
-      </c>
-      <c r="D15" t="n">
-        <v>30</v>
       </c>
       <c r="E15" t="n">
         <v>30</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>30</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>2 paquetes de galletas bajas en azúcar e idealmente sabor a vainilla y sin crema, 1/2 tarro de manjar o 1/2 taza de dulce de leche, 1 1/4 taza de coco rallado, 1/2 taza de leche condensada, 1/2 taza de chocolate en polvo amargo, virutas de chocolate y de colores</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>1-moler los dos paquetes de galletas, idealmente utilizar el procesador de alimentos o la juguera., 2-para las cocadas unir la 1/2 taza de dulce de leche, 1 taza de coco rallado y 1 taza de galletas molidas. unir bien hasta lograr una buena consistencia., 3-formar bolitas pequeñas y pasarlas por el coco rallado restante., 4-para los confites mezclar la leche condensada con el chocolate en polvo amargo., 5-agregar el resto de las galletas en polvo. unir bien y formar bolitas, para luego pasarlas por virutas de chocolate y de colores.</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>23.44028520499108</v>
       </c>
     </row>
@@ -1027,39 +1074,42 @@
       <c r="A16" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="n">
+        <v>24</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Costillar de cerdo con puré picante</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>55</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>1 costillar de cerdo (1 kilo app.), 1 cucharada de mostaza, 1 cucharadita de ajo en polvo, 1 taza de vino blanco, 1 cucharada de aceite de oliva, 2 cucharadas de salsa de tomate, 1 cucharadita de azúcar morena, sal y pimienta, 1 cucharadita de ají color o páprika, 1 cucharadita de tomillo fresco, 1 cucharadita de orégano, 1 kilo de papas, leche, sal, pimientas blanca, mantequilla, ají en pasta, merquén (optativo)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>1-colocar el costillar en un recipiente y esparcir con la mano la cucharada de mostaza sobre éste., 2-en un pequeño bol mezclar el resto de los ingredientes (vino,aceite, salsa, azúcar, sal, pimienta, ají color, tomillo, orégano). verter sobre el costillar y tapar el recipiente con papel de plástico. dejar reposar en el refrigerador un par de horas. dar vuelta un par de veces para que se impregnen los sabores., 3-se puede cocinar directamente en una parrilla. también pueden hornearlo por unos 35 minutos a 400° f (200°c). deben dar vuelta el costillar y pintar con el lïquido de la marinada para que no se reseque., 4-mientras tanto hacemos un puré, cocemos las papas sin cáscara y cortadas en cuadros grandes en agua fría. una vez que empieza a hervir el agua se cuenta aproximadamente unos 15 a 20 minutos., 5-luego se cuelan las papas y se les retira del agua. en una olla calentamos la mantequilla y la leche. mientras tanto, usamos el pasa puré o las molemos con algún utensilio adecuado. una vez molidas las papas, agregamos la mezcla caliente de leche y mantequilla, sazonar con sal y pimienta. luego adjuntamos el ají en pasta y el merquén., 6-finalmente servimos un poco de puré y encima un trozo del costillar.</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>18</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>67.8698752228164</v>
       </c>
     </row>
@@ -1067,39 +1117,42 @@
       <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Empanadas de camarón queso</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>35</v>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>3 tazas de harina para todo uso, sin polvos de hornear, 1 cucharadita de sal, 1 cucharadita de polvos de hornear, 1/2 taza de leche tibia, 2 cucharadas de manteca derretida, 1/2 taza de agua tibia, 1/2 kilo de camarones crudos, 1/2 kilo de queso mantecoso, aceite vegetal para freír</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>1-en un bol grande colocar la harina y hacer como un volcán. alrededor colocar la sal, y en el centro los polvos de hornear, la leche tibia y la manteca. unir la masa y de a poco ir agregando el agua tibia. formar una masa suave y elástica que no se pegue en los dedos. amasar lo suficiente para lograr la masa. luego dejar reposar la masa tapada por unos 10 minutos., 2-estirar la masa con un uslero, debe quedar delgada. puede usar platos de entrada para cortar la masa., 3-colocar en el entorno un poco de agua con los dedos, luego colocar en el centro trozos de camarones y queso, debe llevar más queso que camarón., 4-cerrar la empanada, luego darle un doblez y con la ayuda de un tenedor marcar el entorno como se ve en la foto arriba., 5-si desea hornearla, precaliente el horno a 400°f (200°c). pincelar por encima de la empanada con un poco de la mezcla de yema y agua. hornear por 15 minutos., 6-ahora, si desea hacerlas fritas, calentar bien el aceite a fuego medio por unos 5 minutos. luego colocar el fuego bajo e ir friéndose por unos 5 a 6 minutos por lado. colocar sobre bastante papel absorbente.</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>10</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>39.88413547237077</v>
       </c>
     </row>
@@ -1107,39 +1160,42 @@
       <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="n">
+        <v>27</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Empanadas de mariscos</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>35</v>
-      </c>
-      <c r="D18" t="n">
-        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>8</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>para la masa:, 3 tazas de harina, 70 grs de manteca derretida, 1 taza de leche tibia, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, para el pino, 2 a 3 cucharadas de aceite maravilla o canola, 2 cebollas picadas en cuadros, 1/2 kilo de surtido de mariscos, 1 cucharadita de ají color (puede reemplazar por paprika), 1 cucharadita de ají en pasta, 1/2 cucharadita de orégano, sal a gusto</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>1-comenzamos con el pino, ya que este para rellenar las empanadas debe estar frío., 2-freír la cebolla en un sartén con las cucharadas de aceite. este proceso tomará unos 6 minutos aproximadamente, a fuego medio. debe ir revolviendo de vez en cuando., 3-luego agregar el ají color, ají en pasta, orégano y sal., 4-enseguida agregar los mariscos, revolver bien y dejar cocinar unos 3 minutos más., 5-no debe recocer los mariscos ya que el resto de cocción terminará en el horno., 6-retirar del fuego y dejar que se enfríe completamente antes de usar., 7-para preparar la masa, esta debe quedar super manejable y compacta., 8-coloque en un bol la harina y sal, haga un hoyo en el centro y coloque la manteca derretida, mezcle un poco con una cuchara para que no se queme. agregar la leche tibia, mezclar un poco más con la cuchara para luego comenzar a amasar con las manos sobre la mesa. no es necesario agregar más harina, esta mezcla queda buenísima y no debería pegarse en las manos., 9-forme la masa y divídala en 8 porciones, puede hacerlas más pequeñas si las quiere fritas y así tendrá más porciones. forme bolitas iguales, luego con la ayuda de un uslero, estire cada bolita en forma circular., 10-rellenar con el pino. cerrar los bordes de cada empanada como se ve en las fotos., 11-si las va a hornear, precaliente el horno a 400°f (200°c)., 12-pincelar cada empanada con la mezcla de una yema con un poco de agua o leche., 13-hornear por 20 minutos., 14-si las quiere fritas, prepare una olla o sartén hondo con bastante aceite. debe esperar que esté bien caliente. para saber esto puede usar el truco de colocar un fósforo en el aceite y cuando este se prenta es porque el aceita está óptimo para freír., 15-a las empanadas fritas no se les pincela con la mezcla de yema + agua., 16-recuerde dejar las empanadas bien cerradas para que no se les vaya escapar el jugo del pino, sino le va a sarpicar aceite., 17-freír 2 a 3 minutos por lado., 18-servir con pebre.</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>14</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>48.97504456327985</v>
       </c>
     </row>
@@ -1147,39 +1203,42 @@
       <c r="A19" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" t="n">
+        <v>29</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Empanadas de pino</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>50</v>
-      </c>
-      <c r="D19" t="n">
-        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>12</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>500 grs carne de vacuno picado o molida (puede usar asiento, posta rosada o lomo liso), 2 cebollas grandes, 1 cucharada de aceite, 1 cucharadita de sal, 1/2 cucharadita de ají color (reemplazar por paprika), 1/4 cucharadita de orégano, 1/4 cucharadita de pimienta, 1/4 cucharadita de comino, 3 huevos cocidos y cortados en rodajas, 24 aceitunas negras, 1/2 taza de pasas, 1 kilo de harina, 180 grs de manteca, 1 cucharada de sal, 2 tazas de agua a temperatura de ambiente</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>1-agregue la harina, sal, manteca y el agua poco a poco para ir formando una masa fácil de trabajar., 2-ojo que la manteca no debe derretir. se usa a temperatura de ambiente y se va integrando con las manos o en la mezcladora., 3-una vez lista la masa, estirar con la ayuda de un uslero y cortar círculos de 15 cms de diámetro., 4-precalentar el horno a 200°c (400°f)., 5-en el centro de cada masa poner una o dos cucharadas grandes de pino, una rodaja de huevo, una o dos aceitunas, 2 a 3 pasas., 6-humedecer un borde de la masa para poder cerrarla, luego doblar\xa0 los costados y luego el centro de la empanada., 7-puede pincelar por encima de cada empanada con la mezcla una yema y agua. así le dará un color dorado por encima., 8-hacer un aguajero en el centro de cada empanada con la ayuda de un mondadientes o algo similar., 9-llevar al horno por 20 minutos o hasta que las empanadas estén doradas por encima.</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>16</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>60.87344028520499</v>
       </c>
     </row>
@@ -1187,39 +1246,42 @@
       <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="n">
+        <v>30</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Empolvados chilenos</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>37</v>
-      </c>
-      <c r="D20" t="n">
-        <v>15</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>5 huevos, 1 taza de harina cernida sin polvos de hornear, 1 taza de azúcar granulada, azúcar flor para espolvorear, manjar (dulce de leche)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>1-precalentar el horno a 350°f (180°c), 2-batir las claras un poco, luego comenzar agregar el azúcar. batir hasta que no se sientan los cristales de azúcar., 3-añadir las yemas una a una., 4-luego con una espátula o cuchara integrar la harina de manera envolvente lo necesario para unir., 5-sobre una lata de horno cubierta con papel para hornear se van formando montoncitos de masa, también se puede ayudar con una manga pastelera., 6-hornear por unos 12 minutos aproximadamente o hasta que estén levemente dorados., 7-una vez fríos se pueden pasar cada masa dentro una bolsa ziploc con azúcar flor., 8-se van uniendo de a dos con manjar a gusto.</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>5</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>29.50089126559715</v>
       </c>
     </row>
@@ -1227,39 +1289,42 @@
       <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="n">
+        <v>31</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Ensalada a la chilena</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>10</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>3 tomates medianos, 1 cebolla cortada en pluma, 1 cucharada de perejil picado, aceite y sal a gusto</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>1-en esta primera es opcional, pero si no quiere quedar pasado a cebolla es que sugiero blanquear la cebolla por unos minutos en agua caliente. ponga la cebolla cortada en pluma en un pocillo, la cubre con agua caliente por unos minutos, y luego la lava bajo el chorro de agua., 2-cortar los tomates en gajos, o en rodajas, agregar la cebolla, perejil y aliñar con sal y aceite a gusto., 3-déjela reposar unos minutos para que el tomate vaya botando su jugo.</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>13.99286987522282</v>
       </c>
     </row>
@@ -1267,39 +1332,42 @@
       <c r="A22" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" t="n">
+        <v>34</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Flan de manjar</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>80</v>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
       </c>
       <c r="E22" t="n">
         <v>8</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>1 taza de azúcar, 1 tarro de manjar (380 grs), 8 huevos, 1 litro de leche, 1/2 taza de azúcar (extra)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>1-en un sartén colocar un poco de azúcar, cuando esta comience a tomar color, ir agregando poco a poco toda la taza de azúcar. a medida que se vaya derritiendo vaya revolviendo el azúcar para que vaya tomando el color caramelo y esto debe cocinarse a fuego medio. una vez listo el caramelo, con mucho cuidado debe esparcirlo sobre un molde de 24 cms. con orificio en el centro, por supuesto puede utilizar de otro tipo molde., 2-ahora comenzamos a preparar el flan mientras dejamos que se enfríe el molde en un lugar seguro., 3-para el flan colocar en un bol batir el manjar e ir incorporando los huevos, la 1/2 taza de azúcar y la leche. luego al momento de traspasar la mezcla al molde utilicen un colador., 4-este molde debe ir sobre otra fuente con agua fría (baño maría)., 5-llevar al horno por 1 hora a 350°f (180°c)., 6-puede dejar enfríar en el horno., 7-el molde debe estar completadamente frío antes de desmoldar., 8-una listo, refrigerar.</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>5</v>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>50.57932263814617</v>
       </c>
     </row>
@@ -1307,39 +1375,42 @@
       <c r="A23" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" t="n">
+        <v>37</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Garbanzos con ostiones</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>35</v>
-      </c>
-      <c r="D23" t="n">
-        <v>4</v>
       </c>
       <c r="E23" t="n">
         <v>4</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>2 frascos o tarros de garbanzos cocidos, 40 ostiones limpios, 1 cebolla picada finamente, 1/2 diente de ajo picado, 1/2 tomate, sin piel y rallado, 1/2 taza de vino blanco, 1 cucharada de ají color, hojas de rúcula, aceite de oliva, sal marina y pimienta</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>1-en un sartén hacer un sofrito con la cebolla y un chorro de aceite de olive. a los 5 minutos agregar el ajo picado y sofreír a fuego medio para que no se queme., 2-agregar el ají color, revolver y luego agregar el vino y el tomate rallado. cocinar por unos 10 minutos para evaporar el vino., 3-agregar a este sofrito los garbanzos con todo el jugo de la conserva y cocinar unos minutos para que se evapore parte de este jugo. agregar sal y pimienta a gusto., 4-antes de servir, calentar muy bien una sartén con un poco de aceite y, cuando empiece a humear, poner los ostiones y dejar que se doren bien por una cara. esto tomará un poco más de un minuto si la temperatura es suficientemente alta., 5-dar vuelta y dejar un minuto más. agregar sal y pimienta sobre el guiso de los garbanzos agregando el jugo que se pueda recuperar de la sartén. a último momento decorar con unas hojas de rúcula o perejil como lo hice yo.</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>11</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>42.15686274509804</v>
       </c>
     </row>
@@ -1347,39 +1418,42 @@
       <c r="A24" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" t="n">
+        <v>39</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Hallullas y día de la comida chilena</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>40</v>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
       </c>
       <c r="E24" t="n">
         <v>10</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>3 tazas de harina sin polvos de hornear (420 grs), 1 sobre de levadura en polvo ( 7 grs), 1 cucharadita de azúcar (4 grs), 1 y un poquito más cucharadita de sal (8 grs), 1/2 taza de leche tibia (105°-115°f) (40°-46°c), 1/2 taza de agua tibia (105°-115°f) (40°-46°c), 3 cucharadas de manteca vegetal ( 42 grs) / pueden reemplazar por mantequilla</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>1-disolver la levadura en un poco de agua tibia la temperatura no debe exceder los (115°f) (46°c)., 2-en un bol colocar la harina con la sal y azúcar., 3-agregar la levadura disuelta, leche, agua y la manteca a temperatura de ambiente (si desea puede derretirla también)., 4-trabajar la masa hasta unir bien todos los ingredientes. dejar reposar la masa unos 20 minutos., 5-luego con la ayuda de un uslero extender la masa, para luego doblarla en dos., 6-de esta forma cortamos círculos de tamaño regular. colocamos estos círculos en una bandeja cubierta con papel de mantequilla (idealmente) y pinchamos la masa con un tenedor. dejamos reposar al menos 1/2 hora., 7-precalentar el horno a 400°f (200°c) y luego horneamos por uno 20 minutos como máximo., 8-*como alternativa si quiere que las hallulas le queden doradas y brillantes, puede mezclar una yema de huevo con un poquito de agua y con un pincel las pinta por encima. este paso es totalmente opcional.</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>7</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>35.51693404634581</v>
       </c>
     </row>
@@ -1387,39 +1461,42 @@
       <c r="A25" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" t="n">
+        <v>40</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Helado de borgoña</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>35</v>
       </c>
-      <c r="D25" t="n">
-        <v>6</v>
-      </c>
       <c r="E25" t="n">
         <v>6</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>2 tazas de un buen vino tinto (si es chileno es mejor), 3/4 taza de azúcar granulada, 1 palo de canela (opcional), 1 taza de puré de frutillas (moler las frutillas naturales), 3/4 taza de crema líquida</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>1-en una olla colocar el vino, azúcar, canela. hervir por unos minutos o hasta que el azúcar se haya disuelto. y si desea retirar el alcohol del vino debe dejarlo hervir al menos por unos 8 a 10 minutos más. o usar la técnica de flambeado, pero esto es recomendado para quienes dominan este paso., 2-dejar que esta mezcla se enfríe y retirar el palo de canela., 3-luego unir la mezcla de vino con el puré de frutillas y crema., 4-se puede proceder a usar la máquina de helado o en el caso que no tenga debe guardar la mezcla en un pote de plástico hermético y llevarlo al congelador. después de 2 horas sacarlo y batir la mezcla por unos minutos, y posteriormente guardarlo en el congelador por un par de horas.</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>5</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>28.5204991087344</v>
       </c>
     </row>
@@ -1427,39 +1504,42 @@
       <c r="A26" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" t="n">
+        <v>41</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Helado de cola de mono (trago chileno)</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>20</v>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
       </c>
       <c r="E26" t="n">
         <v>10</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>1 litro de leche líquida, 1 taza de azúcar granulada, 3 cucharaditas de café instantáneo en polvo, 1 taza (240ml) de aguardiente, 5 clavos de olor, 1 pedazo de cáscara de naranja, 1 pizca de nuez moscada en polvo, 1 cucharadita de esencia de vainilla, 2 palitos de canela</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>1-colocar en una olla la leche, azúcar, clavos de olor, cáscara de naranja, nuez moscada y palos de canela. revolver hasta disolver el azúcar. en una taza disolver las 3 cucharaditas de café con un poco de agua caliente. reservar. cuando la leche suelte el primer hervor, apagar el fuego y agregar el café y la esencia de vainilla. dejar enfriar. finalmente agregar el aguardiente. pasar la mezcla por un colador., 2-luego colocar la mezcla en una máquina para hacer helado y seguir la intrucciones del fabricante., 3-en caso de no contar con una máquina, coloque la mezcla en un envase plástico con tapa y la lleva al refrigerador por 2 horas. sacar del freezer y revolver enérgicamente por unos minutos y nuevamente llevar al freezer por varias horas antes de servir.</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>9</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>30.25846702317291</v>
       </c>
     </row>
@@ -1467,39 +1547,42 @@
       <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" t="n">
+        <v>44</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Kuchen de duraznos</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>75</v>
-      </c>
-      <c r="D27" t="n">
-        <v>12</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>12</v>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>1 1/2 taza de harina para todo uso, sin polvos de hornear, 3/4 taza de azúcar granulada, 2 cucharaditas de polvos de hornear, 1/4 cucharadita de sal, 80 grs de taza de mantequilla fría, cortada en cuadros, 1/2 taza de leche, 1 huevo, 3 duraznos frescos pelados o 3 unidades de duraznos en conserva, 1 taza de crema de leche líquida, 1 cucharada de harina, 1/2 taza de azúcar, 1 huevo, 1 cucharadita de esencia de vainilla, 1 pizca de sal</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>1-precalentar el horno a 400°f (200°c)., 2-en un bol mezclar la harina, azúcar, polvos de hornear, sal. agregar la mantequilla para ir uniendo los ingredientes y lograr una especie de miga., 3-en otro bol batir el huevo y la leche. e incorporar a la mezcla anterior de harina. mezclar bien., 4-colocar esta mezcla en un molde de unos 24 cms enmantequillado., 5-colocar encima los duraznos cortados en gajos., 6-llevar al horno a la misma temperatura del precalentado por unos 15 minutos., 7-mientras en un bol mezclar la crema con la harina, evitando que se formen grumos. añadir el azúcar, huevo, esencia de vainilla y sal. mezclar bien., 8-sacar el molde del horno y colocar encima de la masa precocida la mezcla de crema., 9-llevar al horno nuevamente a 350°f (180°c) por unos 40 minutos., 10-tratar que quede dorado por encima., 11-una vez listo, dejar enfríar completamente antes de desmoldar.</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>16</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>73.1283422459893</v>
       </c>
     </row>
@@ -1507,35 +1590,38 @@
       <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" t="n">
+        <v>45</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Kuchen de mermelada</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>55</v>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
       </c>
       <c r="E28" t="n">
         <v>10</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>10</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>2 tazas (280 grs) de harina, 4 cucharadas (40grs) de azúcar flor (glas), 1 cucharadita (4 grs) de polvos de hornear, 1 huevo, 4 cucharadas (60 grs) de mantequilla blanda, ralladura de un limón, 1/2 taza de leche, 200 grs de mermelada del sabor que desee</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
         <v>8</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K28" t="n">
         <v>45.14260249554367</v>
       </c>
     </row>
@@ -1543,39 +1629,42 @@
       <c r="A29" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" t="n">
+        <v>48</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Kuchen de manzana 2</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>70</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>8</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>10</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>250 grs de harina, 170 grs de mantequilla sin sal, 1 cucharadita de sal, 1 cucharada de azúcar granulada, 1 yema de huevo, 6 cucharadas de leche líquida, 4 manzanas verdes idealmente, 20 grs de harina, 80 grs de azúcar rubia, 1 cucharada y media de esencia de vainilla, 1 pizca de nuez moscada, 1 cucharadita de canela en polvo, 1 yema, 20 ml de crema líquida, 1 cucharada de azúcar granulada, 1 pizca de sal, papel de aluminio</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>1-batir la mantequilla con el azúcar, agregar la yema, luego el resto de ingredientes secos (harina y sal) alternando con la leche. obtener una masa homogénea. hacer una bola, envolver en alusa plástico y guardar en refrigerador al menos por una hora. reservar., 2-pelar las manzanas, sacarles el centro y cortalas en rodajas. colocarlas en un bol y agregarles la vainilla., 3-en otro bol mezclar la harina, el azúcar, la nuez moscada y la canela. mezclar bien y adjuntarlo a las manzanas, revolver todo muy bien., 4-sacar la masa del refrigerador, dejar un poco de masa para el enrejado., 5-con el mismo alusa plast estirar la masa con la ayuda de un uslero. colocar la masa estirada en un molde de 22 cm. acomodar bien. luego agregar la mezcla de las manzanas. y con el resto de la masa, estirarla en forma rectángular y cortar huinchas delgadas. colocarlas intercaladas encima del kuchen., 6-mezclar todos los ingredientes y con la ayuda de un pincel, pintar encima del kuchen., 7-llevarlo al horno precalentado a 200° c (400°f) por 15 minutos. luego bajar el fuego a 180° c (350° f) por unos 25 minutos más y en este paso taparlo con papel de aluminio.</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>17</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>72.9500891265597</v>
       </c>
     </row>
@@ -1583,39 +1672,42 @@
       <c r="A30" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" t="n">
+        <v>49</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Kuchen de mora</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>55</v>
-      </c>
-      <c r="D30" t="n">
-        <v>12</v>
       </c>
       <c r="E30" t="n">
         <v>12</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>80 grs.mantequilla, 1/2 taza de azúcar, 1 huevo, 2 tazas de harina cernida, 2 cucharaditas de polvos de hornear, 5 cucharadas de leche fría, 1 tarro de leche condensada, 3 yogurts naturales de 227 grs u 8 oz cada uno aproximadamente, también pueden yogurt griego, 200 grs de moras</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>1-relleno:, 2-mezclar los yogurts con la leche condensada, dejar reposar unos 20 minutos en el refrigerador., 3-masa:, 4-precalentar el horno a 350°f (180°c) batir la mantequilla con el azúcar y el huevo. agregar la harina con polvos de hornear, alternando con la leche., 5-poner en un molde de 23 cms enmantequillado., 6-extender la masa con la mano, dejando una pestaña por los lados., 7-precocer la masa por unos 10 a 15 minutos., 8-agregar las moras directo a la masa y encima cubrir con la mezcla de yogurth y leche condensada., 9-poner al horno nuevamente por unos 20 a 25 minutos, o hasta que la crema no se pegue en los dedos.</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>10</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>49.68805704099822</v>
       </c>
     </row>
@@ -1623,39 +1715,42 @@
       <c r="A31" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" t="n">
+        <v>51</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Kuchen de nuez</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>70</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>12</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>15</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>1/2 taza de mantequilla (100grs), 3/4 taza de azúcar granulada (140 grs), 1 huevo, 1 3/4 taza de harina sin polvos de hornear (200 grs), la ralladura de un limón, 2 tazas de nueces picadas, 1 tarro de leche condensada (397 grs app), 1 yema, 50 grs de mantequilla derretida</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>1-precalentar el horno a 350°f (180°c)., 2-preparar un molde de 24 o 26 cms. enmantequillarlo o rociar con aceite en spray., 3-para preparar la masa, colocar en un bol la mantequilla y el azúcar, batir muy bien durante unos 2 a 3 minutos. luego agregar el huevo entero y la ralladura del limón. mezclar bien y finalmente agregar la harina poco a poco., 4-formar una masa lisa, que no se pegue en las manos., 5-luego con cuidado extender la masa sobre el molde., 6-llevar al horno por unos 15 minutos., 7-mientras tanto preparar el relleno, mezclar las nueces picadas con la leche condensada., 8-agregar la yema de huevo y la mantequilla derretida. unir todo muy bien., 9-colocar este relleno sobre la masa y cubrir con papel de aluminio. llevar al horno por unos 30 minutos. luego retirar el papel de aluminio y llevar al horno nuevamente por unos 10 minutos hasta que esté dorado., 10-servir cuando esté completamente frío.</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>9</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>54.76827094474153</v>
       </c>
     </row>
@@ -1663,39 +1758,42 @@
       <c r="A32" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" t="n">
+        <v>52</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>Leche asada</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>35</v>
-      </c>
-      <c r="D32" t="n">
-        <v>8</v>
       </c>
       <c r="E32" t="n">
         <v>8</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>1 litro de leche, 1 taza (190 grs.app.) de azúcar granulada, 1 cucharadita de vainilla, 6 huevos, caramelo: 3/4 taza de azúcar granulada</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>1-batir los huevos enteros e ir agregando la leche, azúcar y vainilla. llevar a fuego suave hasta que se disuelva el azúcar. retirar., 2-preparar el caramelo: humedezca el azúcar granulada con 3 cucharadas de agua y lleve a fuego suave, hasta que se derrita completamente y tome color rubio, no debe revolver. bañe con este caramelo el fondo y las paredes de un molde., 3-colocar la mezcla de la leche en la fuente o molde y llevar al horno por unos 40 minutos a 400°f (200°c). dejar enfriar en el horno en la medida de lo posible.</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>5</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K32" t="n">
         <v>28.5204991087344</v>
       </c>
     </row>
@@ -1703,39 +1801,42 @@
       <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" t="n">
+        <v>55</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Locos con salsa verde</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>15</v>
-      </c>
-      <c r="D33" t="n">
-        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>1 cebolla mediana picada en cuadros, 1/2 taza de cilantro picado, 1/4 taza de perejil picado, 1/2 taza jugo de limón, sal y pimienta a gusto, 2 cucharadas de aceite de oliva, locos cocidos (2 o 3 unidades por persona), mayonesa a gusto, lechuga a gusto</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>1-juntar cebolla, cilantro, perejil, jugo de limón, sal, pimienta y aceite., 2-mezclar bien y dejar reposar unos 15 min., 3-para montar el plato, colocar de base lechuga, locos , mayonesa en el centro, y sobre cada loco colocar la salsa verde.</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>9</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>27.80748663101605</v>
       </c>
     </row>
@@ -1743,39 +1844,42 @@
       <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" t="n">
+        <v>56</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>Manzanas asadas</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>50</v>
-      </c>
-      <c r="D34" t="n">
-        <v>4</v>
       </c>
       <c r="E34" t="n">
         <v>4</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>4</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>4 manzanas verdes, 2 cucharadas de mantequilla, (está ok si quiere usar margarina), 1 taza de azúcar morena o rubia, esencia de vainilla, agua</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>1-precalentar el horno 400°f (200°c), 2-ahuecar las manzanas con mucho cuidado, hay un accesorio ideal para las manzanas, como el que se ve en la foto arriba, pero si no tiene, use un cuchillo afilado., 3-en cada orificio colocar un poquito de mantequilla, azúcar y vainilla., 4-colocar las manzanas en una fuente con un poco de agua, y si gusta también puede colocar un poco más de azúcar en la base de la fuente., 5-llevar al horno por unos 35 a 40 minutos., 6-se debe formar una especie de caramelo en la base de la fuente, el cual puede usar para el momento de servir la manzana., 7-si desea puede servir este postre tibio acompañado del helado de su preferencia.</t>
         </is>
       </c>
-      <c r="H34" t="n">
-        <v>6</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J34" t="n">
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K34" t="n">
         <v>38.14616755793226</v>
       </c>
     </row>
@@ -1783,39 +1887,42 @@
       <c r="A35" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" t="n">
+        <v>60</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>Paila marina</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>35</v>
       </c>
-      <c r="D35" t="n">
-        <v>6</v>
-      </c>
       <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
         <v>4</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>1 cucharada de aceite, 1/2 unidad de cebolla picada en cuadros finos, ají color, orégano seco, sal y pimienta, 1 kg de almejas con concha, 500 grs de choritos con concha, 4 medallones de pescado (congrio idealmente o algún otro bien firme), 1 taza de vino blanco, 2 a 3 tazas de caldo de pescado o de verduras, 1 taza de tomates en conserva idealmente, gotas de salsa de ají, 150 grs de lenguas de machas (navajuelas también sirven), perejil o cilantro para decorar</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>1-en una olla grande calentar el aceite y freír la cebolla por unos 5 minutos o hasta que esté transparente sin dorar. sazonar con los aliños : ají color, orégano, sal y pimienta a gusto., 2-agregar las almejas y choritos lavados. cocinar por unos 3 minutos., 3-agregar el pescado y cocinar por unos 2 minutos. añadir el vino, caldo, tomates y gotas de salsa de ají., 4-cocinar la mezcla por unos 12 minutos., 5-al final se agregan las machas y se cocinan por unos 3 minutos., 6-servir caliente, idealmente en un plato de greda decorado con perejil.</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>14</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K35" t="n">
         <v>48.97504456327985</v>
       </c>
     </row>
@@ -1823,39 +1930,42 @@
       <c r="A36" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" t="n">
+        <v>61</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>Palta reina</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>35</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>2</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>1 palta (aguacate), 1 pequeño trozo de morrón rojo (opcional), 1/2 pechuga de pollo, 1 a 2 cucharadas de mayonesa, 6 hojas de lechugas, 1 aceituna, sal y pimienta a gusto, aliño para la lechuga: sal, aceite y limón (opcional)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>1-colocar la media pechuga de pollo en el horno a 400°f (200°c) por unos 20 a 25 minutos., 2-una vez listo el pollo, dejar enfríar y cortar en pequeños trozos., 3-mezclar el pollo cortado con una o dos cucharadas de mayonesa, pueden agregar morrón rojo picado fino, aliñar con pimienta también si gustan., 4-picar las hojas de lechuga, y en esta paso pueden aliñarla con sal, aceite y limón (o simplemente la sirven así sin aliñar), luego colocar como base la lechuga en un plato de entrada, encima colocan la mitad de la palta (aguacate) y la cual se rellena con el pollo y sobre el pollo decorar con la mitad de una aceituna.</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>9</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K36" t="n">
         <v>37.61140819964349</v>
       </c>
     </row>
@@ -1863,39 +1973,42 @@
       <c r="A37" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" t="n">
+        <v>62</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>Palta cardenal</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>15</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>1 palta (aguacate), 3/4 taza de camarones limpios y cocidos (yo compré crudos y los salteé en mantequilla), 2 cucharadas mayonesa (de buena calidad), 1/2 cucharada de limón (opcional), perejil o cilantro picado, lechuga picada, 1/2 unidad de tomate, sal a gusto</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>1-en un plato de entrada colocar de base lechuga picada, suficiente para cubrir el plato., 2-cortar la palta (aguacate) por la mitad. retirar el cuesco y con la ayuda de una cuchara retirar con cuidado la cáscara también., 3-en un pequeño bowl mezclar los camarones y mayonesa, si gusta puede agregar un poco de jugo de limón., 4-con esta mezcla rellenar la palta (aguacate)., 5-esparcir perejil o cilantro picado encima., 6-colocar dos gajos de tomate en cada plato.\xa0</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>8</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>25.53475935828877</v>
       </c>
     </row>
@@ -1903,39 +2016,42 @@
       <c r="A38" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" t="n">
+        <v>63</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>Pan amasado versión 01</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>20</v>
-      </c>
-      <c r="D38" t="n">
-        <v>8</v>
       </c>
       <c r="E38" t="n">
         <v>8</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>5 tazas de harina para todo uso y sin polvos de hornear, 5 cucharaditas de manteca a temperatura de ambiente, 1 sobre de levadura en polvo de 7 grs ( es una cuchadara y media), 1 1/2 cucharadita de sal, 1 cucharadita de azúcar granulada, 1 taza de agua a temperatura de ambiente, 1 yema de huevo (opcional)</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>1-colocar la harina en un bol. hacer un hueco en el centro e ir colocando todos los ingredientes., 2-primero la levadura, azúcar, sal , manteca (va así sin derretir) y agua., 3-mezclar cuidadosamente hasta integrar todos los ingredientes., 4-formar una bola y dejar reposar en un bol por 1 o 2 horas., 5-sacar la masa y amasar por un rato., 6-luego dividir la masa en 8 o 10 unidades iguales. ovillar cada trozo, o sea formar con la masa bolas más pequeñas y colocarlas en la lata o bandeja del horno cubierto con papel de mantequilla., 7-dejar reposar nuevamente la masa por una 1/2 hora al menos., 8-precalentar el horno a 375°f (190°c)., 9-luego aplanar con las manos cada pan., 10-es absolutamente opcional pincelar encima de cada pan con yema de huevo batida con un poco de agua o leche., 11-pinchar cada pan con un tenedor encima., 12-hornear por unos 20 minutos., 13-deben quedar dorados por encima.</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>7</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>25.71301247771836</v>
       </c>
     </row>
@@ -1943,35 +2059,38 @@
       <c r="A39" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" t="n">
+        <v>64</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>Pan amasado fácil</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>35</v>
-      </c>
-      <c r="D39" t="n">
-        <v>8</v>
       </c>
       <c r="E39" t="n">
         <v>8</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>500 grs de harina, 7 grs de levadura seca en polvo (21 grs de levadura fresca), 8 grs (1 cucharadita) de azúcar, 8 grs (1 cucharadita) de sal, 80 grs de manteca (usé vegetal, pero pueden usar de cerdo) a temperatura de ambiente, 250 cc de agua tibia</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="n">
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
         <v>7</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>33.06595365418895</v>
       </c>
     </row>
@@ -1979,39 +2098,42 @@
       <c r="A40" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" t="n">
+        <v>66</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Pan marraqueta o pan batido</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>35</v>
-      </c>
-      <c r="D40" t="n">
-        <v>12</v>
       </c>
       <c r="E40" t="n">
         <v>12</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>12</v>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>1 kilo de harina (apróximadamente 8 tazas de harina), 600 cc de agua a temperatura de ambiente, 1 cucharada de sal (14 grs), 15 grs de levadura granulada, 1 cucharadita de azúcar</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>1-en una taza colocar un poco de agua tibia, disolver la levadura junto con el azúcar., 2-dejar reposar 10 minutos., 3-mientras tanto en un bol grande colocar la harina y la sal., 4-agregar la levadura y el agua., 5-formar una masa uniforme y semi blanda.amasar por unos 8 minutos., 6-colocar la masa en un bol grande con un poco de aceite en spray (puede usar mantequilla), 7-dejar fermentar unos 30 minutos., 8-luego dividir la masa en porciones de 100 grs cada uno, puede usar su propia mano para calcular y sacar la porción que sean iguales., 9-ovillar cada porción, se refiere a formar bolitas bien parejas con la palma de la mano y en forma círcular., 10-dejar la masa reposar nuevamente unos 20 minutos., 11-unir de a dos porciones y amasar levemente para que queden más alargados. luego con un accesorio (yo usé mi afilador de cuchillos porque era del grosor perfecto) dividir la masa en el medio como se aprecia en las fotos., 12-ir colocando el pan en una bandeja con papel de mantequilla. otra manera es colocando el pan en una bandeja enmantequillada., 13-precalentar el horno a 400°f (200°c)., 14-idealmente dejar reposar nuevamente el pan por unos 20 minutos al menos, antes de llevarlos al horno., 15-finalmente hornear por unos 18 minutos o hasta que esté dorado el pan por encima a la misma temperatura.</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>5</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>28.5204991087344</v>
       </c>
     </row>
@@ -2019,39 +2141,42 @@
       <c r="A41" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" t="n">
+        <v>67</v>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Pan de pascua</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>85</v>
-      </c>
-      <c r="D41" t="n">
-        <v>12</v>
       </c>
       <c r="E41" t="n">
         <v>12</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>12</v>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t xml:space="preserve">4 tazas de harina, 2 cucharaditas de polvos de hornear, 3 huevos, 1 taza de azúcar flor, 1 taza de leche, 1 cucharada de mantequilla, 1/2 cucharadita de crémor tártaro (opcional) lo venden en tiendas de reposteria, 1/2 cucharadita de bicarbonato, 3 cucharadas de pisco o ron, 1/2 cucharadita de canela en polvo, 1/2 cucharadita de clavo olor en polvo, 1/2 taza de pasas, 1/2 taza de nueces picadas, 1/2 de frutas confitadas, </t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>1-batir las claras ligeramente. reservar., 2-en otro bol batir la mantequilla con el azúcar hasta que esté cremosa. agregar las yemas y luego las claras batidas. mezclar bien., 3-luego agregar los ingredientes secos (harina, bicarbonato, crémor, polvos de hornear) alternando con la leche y el pisco., 4-luego la canela y el clavo de olor., 5-enseguida incorporar las frutas enharinada ( pasas, frutas confitadas y nueces)., 6-vaciar a una molde para pan de pascua o en su efecto un molde de papel como muestro en la foto, esos son ideales también para preparar panettones., 7-hornear a 350° f (180°c) por 1 hora., 8-verificar la cocción interna del pan, clavándole un palo de brocheta por ejemplo, en el centro de la masa. debe salir seco.</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>15</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>75.75757575757575</v>
       </c>
     </row>
@@ -2059,39 +2184,42 @@
       <c r="A42" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" t="n">
+        <v>68</v>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Pan para completo (hot dog)</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>42</v>
-      </c>
-      <c r="D42" t="n">
-        <v>8</v>
       </c>
       <c r="E42" t="n">
         <v>8</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>1 taza de agua (237 ml), 1/4 taza (60 ml) de leche, 2 cucharadas de mantequilla (28 grs), 4\xa0 1/4 taza de harina (600 grs), 2\xa0 1/4 cucharaditas de levadura seca en polvo (7grs), 2 cucharadas de azúcar granulada, 1 1/2 cucharadita de sal, 2 huevos batidos, 1 yema de huevo más 1 cucharada de agua</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>1-en una olla pequeña colocar el agua, leche y mantequilla. no debe hervir esta mezcla. retirar del fuego a lo que se empiece a derretir la mantequilla. si gustan también pueden usar el microondas, por un minuto., 2-luego en un bowl o mezcladora colocar 2 tazas de harina, levadura, azúcar y sal. mezclar bien e ir agregando la mezcla tibia (no caliente) de leche, agua y mantequilla., 3-añadir los huevos batidos y el resto de harina., 4-deben amasar por al menos unos 8 minutos, la masa no debe quedar pegajosa, si eso le pasa, debe\xa0 agregar poquitos de harina extra, hasta lograr una masa pareja y sin que se pegue., 5-formar una bola grande y dejar reposar unos 30 minutos., 6-una vez listo el reposo y que la masa haya aumentado el doble de su volumen, dividirla en 8 porciones iguales., 7-formar con cada porción un rollo alargado de unos 15 cms aproximadamente., 8-dejarlos en una bandeja para que repose unos 20 minutos., 9-precalentar el horno a 200°c (400°f)., 10-batir la yema y agua. pincelar con esta mezcla sobre cada pan., 11-hornear por unos 12 minutos a la misma temperatura.</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>9</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J42" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>41.04278074866311</v>
       </c>
     </row>
@@ -2099,39 +2227,42 @@
       <c r="A43" t="n">
         <v>41</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" t="n">
+        <v>71</v>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Panqueques con manjar</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>25</v>
       </c>
-      <c r="D43" t="n">
-        <v>6</v>
-      </c>
       <c r="E43" t="n">
         <v>6</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>1 taza de harina cernida, 3 huevos, 1 taza de leche, manjar</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>1-batir los 3 huevos enteros, luego agregar la taza de leche y finalmente la harina cernida. revolver hasta que no quede ningún grumo de harina., 2-calentar el sartén con una gota de aceite. echar de cucharadas. se puede utilizar el cucharón y una porción de este estaría bien por porción. una vez que se despeguen las orillas voltear el panqueque, para cocinarlo por el otro lado, esto dura un minuto apróximadamente., 3-retirar el panqueque del sartén, luego extender el panqueque en un plato y rellenarlo con suficiente manjar y enrollar.</t>
         </is>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>4</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K43" t="n">
         <v>21.3458110516934</v>
       </c>
     </row>
@@ -2139,39 +2270,42 @@
       <c r="A44" t="n">
         <v>42</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" t="n">
+        <v>73</v>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Pastel de choclo en masa</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>102</v>
-      </c>
-      <c r="D44" t="n">
-        <v>8</v>
       </c>
       <c r="E44" t="n">
         <v>8</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>1 taza y 1/2 (180grs.) de harina sin polvos de hornear, 1/2\xa0cucharadita de sal, 110\xa0grs de mantequilla sin sal fría cortada en pequeños trozos, 40\xa0ml de agua fría, papel de plástico, 900\xa0grs. de choclo congelado dulce, 1/2\xa0taza de leche líquida, 6\xa0hojas albahaca, sal a gusto, 400 grs de carne molida, 1\xa0cebolla, 1\xa0o 2 dientes de ajo, 1/4 cucharadita de comino, 2\xa0cucharadas de aceite, 3\xa0cucharadas de pasas, 8\xa0aceitunas, 2\xa0huevos duros, aliños para el pino a gusto: sal, pimienta, orégano, ají color., 1/2\xa0cucharadita de harina (opcional)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>1-idealmente en el procesador de alimentos (sino simplemente se trabaja en un bol a mano)., 2-mezclar la harina, sal y azúcar., 3-agregar la mantequilla cortada en pequeños trozos e ir pulsando poco a poco. ( también se puede usar los dedos y se debe ir incorporando la mantequilla para mezclar bien con los ingredientes secos)., 4-luego se agrega el agua., 5-una vez unidos bien todos los ingredientes se forma una bola y se envuelve la masa en el papel de plástico y se lleva al refrigerador por una hora., 6-pasada la hora, se precalienta el horno a 400°f (200°c)., 7-se retira del refrigerador la masa y con la ayuda del mismo papel de plástico se extiende en un molde de 26 cm. dejando unos pequeños bordes., 8-hornear por unos 12 minutos., 9-se pasa el choclo por un procesador de alimentos o licuadora., 10-una vez molido el choclo se coloca en una olla., 11-se agregan las hojas de albahaca y con una cuchara de madera se va revolviendo hasta que comience a hervir, se va alternando con la leche restante., 12-lo ideal es que se vea el fondo de la olla o que espese lo suficiente., 13-sazonar con sal, algunas personas les agregan en este punto un poco de azúcar., 14-reservar., 15-se corta la cebolla en cuadros finos, el ajo también y se fríen en un sartén hasta que esté dorada la cebolla., 16-luego se agrega la carne molida, los aliños y las pasas., 17-\xa0si esta preparación se seca mucho, se puede agregar un poco de agua o caldo de carne., 18-cocinar por unos 15 minutos a fuego medio bajo., 19-si cocción de la carne queda muy líquida se espesa con la cucharadita de harina., 20-idealmente dejar reposar el pino hasta que esté frío., 21-encender el horno a 200°c\xa0 (400°f) nuevamente., 22-una vez precocida la masa se coloca el pino de carne y se distribuye bien., 23-sobre este pino se pone rodajas de huevo cocido y aceitunas., 24-luego se cubre la pastelera y se lleva al horno por 15 minutos o hasta que esté dorado por encima., 25-de manera opcional antes de ponerlo en el horno pueden rociar por encima con azúcar granulada.</t>
         </is>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>22</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2179,39 +2313,42 @@
       <c r="A45" t="n">
         <v>43</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" t="n">
+        <v>74</v>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Pastel de papas</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>85</v>
-      </c>
-      <c r="D45" t="n">
-        <v>4</v>
       </c>
       <c r="E45" t="n">
         <v>4</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>4</v>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>1 kilo de papas, 1/2 taza de leche tibia, 2 cucharadas grandes de margarina o mantequilla derretida, 300 grs de carne molida, 1 diente de ajo, 1 cebolla, aliños: sal, pimienta, orégano, comino y ají color (paprika), 3 huevos, 1 a 2 cucharadas de pasas, 1/2 taza de aceitunas</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>1-pelar las papas, cortarlas en cuadros grandes y se cuece en agua caliente por 15 minutos o cuando estén suficientemente blandas. luego retirar el agua, moler las papas e ir agregando leche tibia, margarina y sal. reservar., 2-en una olla se cuecen los huevos por 10 minutos desde que empiece hervir el agua., 3-en un sartén con aceite freír el ajo picado fino junto con la cebolla picada en cuadritos, cuando estén dorados agregar la carne y el resto de aliños. finalmente agregar las pasas. mezclar todo muy bien., 4-luego en una fuente que pueda ir al horno, colocar el pino (lo que hizo en el sartén), los huevos cortados en rodajas, las aceitunas y finalmente el puré. se puede colocar encima del pastel, azúcar granulada o queso, pero eso es totalmente opcional., 5-se lleva al horno por unos 15 minutos como máximo.</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>13</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>71.21212121212122</v>
       </c>
     </row>
@@ -2219,39 +2356,42 @@
       <c r="A46" t="n">
         <v>44</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" t="n">
+        <v>75</v>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Pebre chileno</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>10</v>
       </c>
-      <c r="D46" t="n">
-        <v>6</v>
-      </c>
       <c r="E46" t="n">
         <v>6</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>6</v>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>1 tomate grande picado en cuadros pequeños, 1 cebolla mediana picada en cuadros pequeños, 2 dientes de ajos picados, 3 cucharadas de perejil picado, 3 cucharadas de cilantro picado, 1 trozo de ají verde picado, 1 cucharada de ají rojo en pasta, 2 cucharadas de aceite vegetal o de oliva light, sal y pimienta a gusto, 1 pequeño chorrito de vino blanco</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>1-mezclar todos los ingredientes en un bol y dejar reposar una media hora al menos., 2-rectificar el sabor y añadir más sal si es necesario., 3-en este momento pueden pasarlo por una picadora, si desean servirlo molido, sino lo dejan tal cual., 4-servir acompañado de pan tibio con mantequilla. aunque pueden servirlo para acompañar carnes o el plato que deseen, con las empanadas quedan espectaculares.</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>10</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>27.62923351158645</v>
       </c>
     </row>
@@ -2259,39 +2399,42 @@
       <c r="A47" t="n">
         <v>45</v>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" t="n">
+        <v>77</v>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>Picarones con chancaca</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>35</v>
       </c>
-      <c r="D47" t="n">
-        <v>6</v>
-      </c>
       <c r="E47" t="n">
         <v>6</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>6</v>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>400 grs de zapallo (calabaza) cocido y molido, 1 kilo de harina sin polvos de hornear, 3 cucharaditas de polvos de hornear, 1 huevo grande, 3 cucharadas de azúcar granulada, 1/2 kilo de chancaca (panela), 5–6 clavos de olor, cáscaras de naranja, 1 cucharadita de azúcar, 1 cucharadita de café instántaneo disuelto en un poco de agua, 2 cucharaditas de maicena disuelta en un poco de agua fría, 3/4 litro de agua fría</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>1-una vez cocido el zapallo se pasa por un pasa puré, y se mezcla con la harina, polvos de hornear, azúcar granulada y el huevo entero. trabajar la masa con las manos e ir agregando más harina si fuese necesario. formar una masa blanda y que no se pegue en los dedos., 2-dejar reposar una media hora., 3-idealmente con las manos frías ir formando bolitas y con la ayuda de los dedos vamos haciendo un agujero en centro. mientras tanto calentamos un sartén con abundante aceite., 4-se comienzan a freír y se retiran cuando estén levemente dorados por ambos lados., 5-se estilan y se colocan en un plato con papel absorvente para poder retirar el exceso de aceite., 6-también preparamos la salsa, en una olla colocamos la chancaca, cáscara de naranjas, clavos de olor, azúcar y agua fría. dejamos que se comience a disolver la chancaca, y vamos revolviendo ocasionalmente., 7-cuando ya comience a hervir la salsa, agregamos la maicena disuelta en un poco de agua y finalmente añadimos el café el cual le da un toque especial mejorando notablemente el gusto., 8-servimos los picarones bañados en la salsa.</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>12</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>44.4295900178253</v>
       </c>
     </row>
@@ -2299,39 +2442,42 @@
       <c r="A48" t="n">
         <v>46</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" t="n">
+        <v>79</v>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Pie de limón</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>48</v>
-      </c>
-      <c r="D48" t="n">
-        <v>12</v>
       </c>
       <c r="E48" t="n">
         <v>12</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>12</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>1 tarro de leche condensada, 4 huevos, el jugo de 2 limones, ralladura de un limón, 6 cucharadas colmadas de harina, 10 cucharadas colmadas de ázucar granulada, 3 cucharaditas colmadas de polvos de hornear, 40 grs. de margarina o mantequilla blanda, 2 cucharadas de leche fría</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>1-relleno: batir muy bien 3 yemas, agregar de poco el tarro de leche condensada, luego el jugo de limón y la ralladura. poner en espera al refrigerador., 2-masa: unir la harina, 3 cucharadas de ázucar granulada, los polvos de hornear, 40 grs margarina, un huevo entero y la leche muy bien con las manos; si es necesario agregar poquitos de harina para que no se pegue en las manos. extender en un molde de 28 cm. enmantequillado y pinchar con un tenedor la masa. hornear casi completamente ( por unos 10 minutos a 350°f/180°c)., 3-sacar del horno, vaciarle encima el relleno y nuevamente al horno por unos 5 minutos como máximo. sacarlo otra vez del horno y colocar el merengue por unos 3 minutos hasta que este dorado., 4-merengue: en una olla o sartén colocar el azúcar restante con un poco de agua, mientras tanto batir las claras a nieve y cuando el azúcar esté disuelta y este formado un almibar claro agregar en forma de hilo o sea muy de a poco a las claras batidas. se deja de batir cuando las claras estén frías., 5-luego se montan sobre el pie, y puede colocarlo al horno para que se dore o si tienen soplete pueden usarlo sin necesidad de colocar el pie con el merengue en el horno.</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>9</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>43.98395721925134</v>
       </c>
     </row>
@@ -2339,39 +2485,42 @@
       <c r="A49" t="n">
         <v>47</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" t="n">
+        <v>81</v>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Pollo arvejado</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>45</v>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
       </c>
       <c r="E49" t="n">
         <v>4</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>4 trutos (presas) de pollo, 1/2 unidad de pimentón rojo, 2 dientes de ajo, 1 cebolla grande, 2 zanahorias, 1 taza de arvejas, 100 cc de vino blanco, sal a gusto, pimienta a gusto, 1/2 cucharadita de ají color o paprika, 1 hoja de laurel, 2 cucharadas de aceite, 1 taza de caldo de pollo o agua</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>1-en un sartén con aceite freír por unos instantes el pollo por ambos lados. retirar y reservar., 2-en el mismo u otro sartén con aceite la cebolla en pluma, el ajo picado fino, pimentón en cuadros, la zanahoria en rodajas. luego agregar los aliños: sal, pimienta, ají color o paprika. añadir las arvejas y el vino. la hoja de laurel y finalmente el pollo. agregar el caldo de pollo o agua para que no se seque., 3-se cuece con la olla tapada a fuego medio/bajo por 30 minutos o hasta que el pollo esté completamente cocido., 4-*servir con arroz blanco o papas fritas o papas doradas.</t>
         </is>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>13</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K49" t="n">
         <v>51.60427807486632</v>
       </c>
     </row>
@@ -2379,39 +2528,42 @@
       <c r="A50" t="n">
         <v>48</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="n">
+        <v>82</v>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Ponche a la romana</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>5</v>
-      </c>
-      <c r="D50" t="n">
-        <v>10</v>
       </c>
       <c r="E50" t="n">
         <v>10</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>10</v>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>1 botella de champagne, 1 litro de helado de piña, 1 piña natural o un tarro en conserva</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>1-colocar en cada copa uno o dos porciones de helado de piña, agregar piña picada y finalmente completar con champagne.</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>3</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>9.269162210338679</v>
       </c>
     </row>
@@ -2419,39 +2571,42 @@
       <c r="A51" t="n">
         <v>49</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" t="n">
+        <v>84</v>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>Porotos con riendas versión 02</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>35</v>
       </c>
-      <c r="D51" t="n">
-        <v>6</v>
-      </c>
       <c r="E51" t="n">
         <v>6</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">1 taza de porotos burros ( o 2 tarros de porotos, estos vienen cocidos y listo para usar), 1 taza apróximadamente de zapallo camote cortado en cuadros, 1/2 taza de choclo (maíz) desgranado (pueden usar congelado), 1 diente de ajo, 6 hojas de albahaca, 1 trozo de pimentón rojo (morrón), sal a gusto, 1/2 cucharadita de comino, 1/3 de taza de salsa de tomate, 1/2 cebolla cortada en cuadros, 1 cucharada de aceite, 1 puñado de tallarines quebrados en dos, </t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>1-si usa los típicos porotos, en una olla se cuecen con agua hervida por unos 25 minutos. cuando a esta cocción le queden unos 15 minutos agregar el zapallo cortado en cuadros, y cuando a esta misma cocción le queden unos 11 minutos agregar los tallarines partidos en dos. finalmente cuando a esta cocción le queden 5 minutos agregar el choclo (maíz). reservar., 2-si usa los porotos que vienen cocidos los pone un bol. mientras tanto en una olla con agua hervida le da cocción al zapallo, tallarines y choclo, en los mismos tiempos que indique antes. cuando esté todo cocido, agregar los porotos. reservar., 3-mientras tanto hacer un sofrito con la cebolla y un poco de aceite. en un montero moler el ajo, albahaca, pimentón, sal y comino. cuando esté listo allí mismo agregar la salsa de tomate, unir., 4-luego vacíar esta mezcla al sofrito de cebolla, cocinar unos 3 minutos. y finalmente añadir este sofrito a la mezcla de porotos y resto de ingredientes. dejar reposar antes de servir.</t>
         </is>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>14</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J51" t="n">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K51" t="n">
         <v>48.97504456327985</v>
       </c>
     </row>
@@ -2459,39 +2614,42 @@
       <c r="A52" t="n">
         <v>50</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" t="n">
+        <v>86</v>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Postre de sémola y manzana</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>50</v>
       </c>
-      <c r="D52" t="n">
-        <v>6</v>
-      </c>
       <c r="E52" t="n">
         <v>6</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>6</v>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>3 manzanas grandes idealmente verdes, 1 cucharadita de canela en polvo, 1/4 taza de azúcar granulada para las manzanas, 1 cucharadita de mantequilla, 2 1/2 tazas de leche, 3/4 taza de sémola, 1/2 taza de azúcar granulada para la sémola, 3 claras de huevos (100 cc aproximadamente), \xa01 taza de azúcar granulada (190 grs)</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>1-pelar las manzanas, luego pasarlas por un rallador. colocar las manzanas ralladas en un bowl, agregar el azúcar junto con la canela, dejar reposar por unos 20 minutos al menos., 2-llevar la mezcla de las manzanas a un sartén con la mantequilla. cocinar unos 4 minutos. si quedan con mucho jugo, les pueden agregar un poquito de maicena para que espese. dejar enfríar., 3-hervir la leche junto con el azúcar, cuando esté a punto de ebullición bajar el fuego al mínimo y con la ayuda de un batidor manual agregar cuidadosamente la sémola para que no se hagan grumos. mezclar bien. luego se coloca en una fuente como base y dejar hasta que se enfríe., 4-batir las claras un poco con el azúcar en un bowl, luego llevarlo a baño maría y batir hasta que se disuelva el azúcar y las claras estén firmes., 5-enseguida se agregan las manzanas encima de la sémola, luego agregamos el merengue., 6-si desea con la ayuda de un soplete puede quemar un poco el merengue por encima para darle un poco de color.</t>
         </is>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>9</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J52" t="n">
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K52" t="n">
         <v>44.96434937611409</v>
       </c>
     </row>
@@ -2499,31 +2657,34 @@
       <c r="A53" t="n">
         <v>51</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" t="n">
+        <v>90</v>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>Queque de manjar</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>75</v>
-      </c>
-      <c r="D53" t="n">
-        <v>12</v>
       </c>
       <c r="E53" t="n">
         <v>12</v>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>12</v>
+      </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
         <v>1</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>duracion Larga</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>39.03743315508022</v>
       </c>
     </row>
@@ -2531,35 +2692,38 @@
       <c r="A54" t="n">
         <v>52</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" t="n">
+        <v>91</v>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>Sagú nora</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>40</v>
       </c>
-      <c r="D54" t="n">
-        <v>6</v>
-      </c>
       <c r="E54" t="n">
+        <v>6</v>
+      </c>
+      <c r="F54" t="n">
         <v>8</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>1 litro de vino tinto, 2 palitos de canela, 1/2 litro de agua hervida, 1 taza de sagú (tapioca), 1 1/2 taza de azúcar, 1 litro de leche, 1 taza de azúcar, 1 chorrito de escencia de vainilla, 4 clavos de olor, 1 palito de canela, 3 yemas</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
         <v>11</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J54" t="n">
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K54" t="n">
         <v>44.6078431372549</v>
       </c>
     </row>
@@ -2567,39 +2731,42 @@
       <c r="A55" t="n">
         <v>53</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" t="n">
+        <v>92</v>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>Salsa verde opción 01</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>5</v>
       </c>
-      <c r="D55" t="n">
-        <v>6</v>
-      </c>
       <c r="E55" t="n">
         <v>6</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>6</v>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>4 cucharadas apróximadamente de perejil picado, 4 cucharadas apróximadamente de cilantro picado, 1 diente de ajo grande, 1 cucharadita de jugo de limón, 1/2 unidad de cebolla o 1 cebolla chica, 2 cucharadas de aceite vegetal, sal y pimienta a gusto, 2 cucharadas de mayonesa light idealmente</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>1-mezclar todos los ingredientes en la picadora o licuadora. rectificar el sabor con sal y pimienta., 2-se puede conservar 2 días después de hecha en el refrigerador., 3-ideal para acompañar el pan, carnes, ensaladas., 4-sale un poco más de una taza apróximadamente de salsa.</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>8</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>20.63279857397504</v>
       </c>
     </row>
@@ -2607,39 +2774,42 @@
       <c r="A56" t="n">
         <v>54</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" t="n">
+        <v>93</v>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Sandía con harina tostada</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>35</v>
       </c>
-      <c r="D56" t="n">
-        <v>6</v>
-      </c>
       <c r="E56" t="n">
         <v>6</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>1 trozo de sandía entero o cortado en pequeños trozos., harina tostada</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>1-simplemente espolvorear harina tostada sobre la sandía y disfrutar.</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>2</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J56" t="n">
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K56" t="n">
         <v>21.70231729055259</v>
       </c>
     </row>
@@ -2647,39 +2817,42 @@
       <c r="A57" t="n">
         <v>55</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" t="n">
+        <v>95</v>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>Sémola con salsa de caramelo</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>35</v>
       </c>
-      <c r="D57" t="n">
-        <v>6</v>
-      </c>
       <c r="E57" t="n">
         <v>6</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="n">
+        <v>6</v>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>3/4 taza de azúcar granulada, 1/4 taza de agua, 1 cucharadita de jugo de limón, 1 litro de leche, 3/4 taza de sémola, 3/4 de taza de azúcar granulada, palos de canela</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>1-en una olla colocar el azúcar con el agua a fuego medio, cuando comience a hervir agregar el jugo de limón., 2-mezclar un poco y dejar que el azúcar comience a trabajar. debe tener cuidado porque la olla estará súper caliente. este proceso para formar un caramelo de color café toma al menos unos 10 minutos. el limón ayudará a no formar los cristales de azúcar, con ello obtendremos un caramelo liso y parejo., 3-una vez listo con mucho cuidado colocar el caramelo en el molde que utilizarán, yo usé un molde rectángular., 4-esparcir con el mismo caramelo ladeando el molde para lograr cubrir por los costados., 5-hervir la leche con los palitos de canela y el azúcar., 6-cuando este a punto de hervir, bajar el fuego al mínimo y agregar con cuidado la sémola, revolviendo bien para que se disuelva y no se formen grumos, también se pueden ayudar con un batidor manual, pero para revolver no para batir., 7-una vez bien incorporada la sémola y fijándose que la mezcla suelta el hervor (o sea que está hirviendo) retirar del fuego, vaciar en el molde con caramelo y dejar enfriar por un par de horas.</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>7</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J57" t="n">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K57" t="n">
         <v>33.06595365418895</v>
       </c>
     </row>
@@ -2687,39 +2860,42 @@
       <c r="A58" t="n">
         <v>56</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" t="n">
+        <v>96</v>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>Sémola con salsa de vino</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>35</v>
       </c>
-      <c r="D58" t="n">
-        <v>6</v>
-      </c>
       <c r="E58" t="n">
         <v>6</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>6</v>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>3/4 taza de sémola, 4 tazas de leche fría, 3/4 de taza de azúcar granulada, palos de canela, 2 1/2 tazas de vino tinto, palos de canela, 1 trozo de cáscara de limón, 3/4 taza de azúcar granulada</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>1-hervir la leche con los palitos de canela y el azúcar. cuando este a punto de hervir, bajar el fuego al mínimo y agregar con cuidado la sémola, revolviendo bien para que se disuelva y no se formen grumos, también se pueden ayudar con un batidor manual, pero para revolver no para batir., 2-una vez bien incorporada la sémola y fijándose que la mezcla suelta como globitos (o sea que esta hirviendo) retirar del fuego, vaciar en un molde y dejar enfriar., 3-colocar en una olla el vino a fuego medio fuerte, cuando comience a hervir, encender con un fósforo o encendedor para que el vino prenda y con ello quemar el alcohol. en este procedimiento hay que tener mucho cuidado. (esto es lo que se llama flambeado)., 4-el flambeado se apaga solo y dura muy poco. luego de haber hecho eso, se agrega los palos de canela, cáscara de limón y azúcar. se espera hasta que el azúcar este bien disuelta., 5-luego se retira del fuego y se deja enfriar., 6-una vez ambas partes enfriadas, se sirve como se visualiza en la foto.</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>8</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J58" t="n">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K58" t="n">
         <v>35.33868092691623</v>
       </c>
     </row>
@@ -2727,39 +2903,42 @@
       <c r="A59" t="n">
         <v>57</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" t="n">
+        <v>98</v>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>Sopaipillas</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>35</v>
       </c>
-      <c r="D59" t="n">
-        <v>6</v>
-      </c>
       <c r="E59" t="n">
         <v>6</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="n">
+        <v>6</v>
+      </c>
+      <c r="G59" t="inlineStr">
         <is>
           <t>3 1/2 tazas de harina, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, 1/4 de kilo de zapallo (250 grs), 3 cucharadas de manteca, aceite para freír</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>1-juntar la harina, los polvos de hornear y sal en un bowl. mientras tanto cocinar el zapallo la primera alternativa es que lo haga en una olla con agua hasta que esté sumamente blando o también con trozos ya partidos de zapallo colocarlo en la bandeja del\xa0 horno por unos 25 mins a 350°f (180°c) para luego pasarlo por cedazo (colador) y así agregarlo a la mezcla de la harina,\xa0 luego se adjunta la manteca derretida., 2-formar una masa lisa que no se pegue en las manos., 3-enseguida con la ayuda de un uslero estirar la masa e ir cortando círculos, del diámetro que ustedes quieran., 4-calentar la sartén con el aceite y luego ir friendo brevemente las sopaipillas por cada lado. muy importante es colocarlas en papel absorvente después., 5-se pueden espolvorear con ázucar flor, servirlas con pebre o pasarlas por chancaca., 6-preparación de la chancaca: disolver la chancaca en una olla con un poquito de agua , agregar un trozo de cáscara de naranja y unos palos de canela. debe quedar una consistencia espesa.</t>
         </is>
       </c>
-      <c r="H59" t="n">
-        <v>6</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J59" t="n">
+      <c r="I59" t="n">
+        <v>6</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>30.79322638146167</v>
       </c>
     </row>
@@ -2767,39 +2946,42 @@
       <c r="A60" t="n">
         <v>58</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" t="n">
+        <v>99</v>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>Sopaipillas pasadas</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>35</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>25</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>30</v>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>3 tazas de harina, 1 cucharadita de polvos de hornear, 1 cucharadita de sal, 1 taza de zapallo, 3 cucharadas de manteca o mantequilla, aceite para freír, 1 paquete de chancaca (225 grs), 1 trozo de cáscara de naranja, 3 clavos de olor, 2 tazas de agua, 1 cucharada de maicena (almidón de maíz)</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>1-en un bowl mezclar el zapallo cocido, harina, sal, polvo de hornear, manteca derretida, unir todo hasta formar una masa homogénea., 2-luego extender sobre una superficie y estiramos la masa con la ayuda de un uslero y dejar la masa de 1 cm de grosor., 3-cortar círculos del tamaño deseado., 4-pinchar con el tenedor y luego freír con abundante aceite caliente, luego mantener a fuego medio. freír por ambos lados hasta que tome color., 5-una vez listas dejarlas en papel absorbente., 6-colocar en una olla la chancaca, agua, cáscara de naranja y clavos de olor., 7-cuando la chancaca esté disuelta, revolver bien y agregar la maicena disuelta en un poquito de agua fría. ir revolviendo y luego al primer hervor apagar el fuego., 8-colocar una par de sopaipillas en la olla, dejarlas unos minutos y servir inmediatamente.</t>
         </is>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>11</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J60" t="n">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K60" t="n">
         <v>42.15686274509804</v>
       </c>
     </row>
@@ -2807,39 +2989,42 @@
       <c r="A61" t="n">
         <v>59</v>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" t="n">
+        <v>101</v>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>Tomaticán</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>45</v>
-      </c>
-      <c r="D61" t="n">
-        <v>4</v>
       </c>
       <c r="E61" t="n">
         <v>4</v>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>1 cucharada de aceite, 4 tomates medianos, 2 o 3 choclos medianos, 1 cebolla española cortada en pluma, 1 diente de ajo picado, 300 grs de posta o asiento cortado en tiras, 1/2 cucharadita de ají color, puede ser un poco más, 1/2 cucharadita de orégano, 1 trozo de morrón verde picado en pequeños cuadros, 2 tazas de caldo de carne o agua (también puede usar una taza de agua y taza de vino blanco), sal y pimienta a gusto, 1/2 cucharadita de ají color, 1/2 cucharadita de orégano</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>1-en un sartén o directamente en una olla freír la cebolla cortada en pluma con el aceite por unos 3 minutos aproximadamente., 2-luego agregar la carne, saltear por unos 2 minutos y añadir el morrón verde. cocinar por 1 minuto. enseguida agregar los choclos desgranados y el tomate cortado en cuadros chicos, si gusta puede pelar el tomate, en mi caso no lo hice porque es en la cáscara donde se concentra la mayor cantidad de nutrientes., 3-añadir los aliños, revolver bien y agregar el agua o caldo de carne o vino blanco. en esta ocasión yo lo hice solo con agua a temperatura de ambiente., 4-tapar la olla o sartén y cocinar por unos 10 minutos., 5-tratar de no recocer ya que los ingredientes pierden su sabor y la textura adecuada., 6-disfrutar acompañado de arroz blanco y perejil picado., 7-si desea puede acompañarlo también con papas cocidas.</t>
         </is>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>14</v>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J61" t="n">
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K61" t="n">
         <v>53.87700534759358</v>
       </c>
     </row>
@@ -2847,31 +3032,34 @@
       <c r="A62" t="n">
         <v>60</v>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" t="n">
+        <v>102</v>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>Tomate relleno</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>35</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
         <v>1</v>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J62" t="n">
+      <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K62" t="n">
         <v>19.42959001782531</v>
       </c>
     </row>
@@ -2879,39 +3067,42 @@
       <c r="A63" t="n">
         <v>61</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" t="n">
+        <v>104</v>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>Torta de galletas</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>25</v>
-      </c>
-      <c r="D63" t="n">
-        <v>8</v>
       </c>
       <c r="E63" t="n">
         <v>8</v>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="n">
+        <v>8</v>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>4 paquetes de galletas baja en azúcar y sin relleno (pueden usar galletas de vino mckay), 600 grs de manjar/dulce de leche, 1/2 taza de leche, coco rallado, cobertura de chocolate para decorar (opcional)</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>1-pueden utilizar un molde rectangular o cuadrado pequeño, deben cubrirlo con papel para hornear. así será más desmoldar., 2-colocar una base con galletas las cuales se deben ir pasando por leche a medida que se vaya armando la torta, no se trata de remojarlas, es simplemente una leve pasada., 3-se va poniendo una capa de galletas, luego una de manjar y así sucesivamente., 4-si se rompe alguna galleta ahí se van acomodando, al final queda todo tapado por el manjar., 5-hay que dejarla en el refrigerador al menos 2 horas., 6-luego al desmoldarla pueden cubrirla con manjar y decorarla por los costados con galletas molidas, coco rallado y encima una idea podría ser derretir chocolate de cobertura y dccorar encima de la torta como sea su gusto o como se ve en la foto.</t>
         </is>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>5</v>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J63" t="n">
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K63" t="n">
         <v>23.61853832442068</v>
       </c>
     </row>
@@ -2919,39 +3110,42 @@
       <c r="A64" t="n">
         <v>62</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" t="n">
+        <v>106</v>
+      </c>
+      <c r="C64" t="inlineStr">
         <is>
           <t>Torta de merengue lúcuma</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>35</v>
-      </c>
-      <c r="D64" t="n">
-        <v>25</v>
       </c>
       <c r="E64" t="n">
         <v>25</v>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" t="n">
+        <v>25</v>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>400 cc app. (8 claras) de huevos a temperatura de ambiente, 2 tazas de azúcar granulada, 1 pizca de sal, 1 cucharada de maicena, 1 cucharada de polvos de hornear, 400 grs de pulpa de lúcuma, 600 ml de crema líquida para batir, papel mantequilla, 3/4 taza de chocolate chips</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>1-pre-calentar el horno a 100°c (200°f). dejar lista una bandeja forrada con el papel de mantequilla, pero antes marcar con un lápiz 3 o 4 círculos de 24 cms de díametro con la ayuda de una tapa de olla, como se aprecia en la segunda foto., 2-en un bol agregar a las claras la pizca de sal y luego batir las claras a punto de nieve idealmente con la batidora, agregar poco a poco el azúcar granulada y batir hasta que cuando toquen con los dedos el batido no se sienta el azúcar. finalmente agregar los polvos de hornear y la maicena., 3-pasar el batido a una manga pastelera o a una bolsa ziploc, a la cual le pueden cortar una punta. y comienzan cuidadosamente a formar un disco sobre la bandeja forrada con el papel de mantequilla, como se aprecia en la foto de arriba., 4-llevar al horno por 2 horas, es muy importante que el horno no supere los 100°c (200°f)., 5-cuando los discos estén secos es porque ya están listos. y una vez fríos, comenzamos a rellenar., 6-en un bol batimos la crema y vamos agregando el puré de lúcuma. mezclamos bien., 7-y encima de un disco de merengue colocamos un capa generosa de crema. enseguida ponemos otro disco de merengue y realizamos el mismo paso que el anterior hasta finalizar, decoramos por fuera de la torta con la crema., 8-la decoración de encima la dejo a su gusto., 9-como indico en la introducción del post, utilicé chocolate chips derretido para decorar.</t>
         </is>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>9</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J64" t="n">
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K64" t="n">
         <v>37.61140819964349</v>
       </c>
     </row>
@@ -2959,39 +3153,42 @@
       <c r="A65" t="n">
         <v>63</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" t="n">
+        <v>107</v>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>Torta de merengue y frutilla</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>35</v>
       </c>
-      <c r="D65" t="n">
-        <v>6</v>
-      </c>
       <c r="E65" t="n">
         <v>6</v>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="n">
+        <v>6</v>
+      </c>
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">400 cc app. (8 claras) de huevos a temperatura de ambiente, 1 1/2 taza (300 grs.) de azúcar granulada, 1 pizca de sal, 1 cucharada de maicena, 1/4 de cucharadita de cremor tártaro, 350 grs de frutillas frescas, 600 ml de crema líquida para batir, 1 taza de azúcar flor cernida (fina) (140 grs.), papel mantequilla, </t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>1-pre-calentar el horno a 100°c (200°f). dejar lista una bandeja forrada con el papel de mantequilla., 2-en un bol agregar a las claras la pizca de sal y luego batir las claras a punto de nieve idealmente con la batidora, agregar poco a poco el azúcar granulada y batir hasta que cuando toquen con los dedos el batido no se sienta el azúcar. finalmente agregar el cremor tártaro y la maicena., 3-pasar el batido a una manga pastelera o a una bolsa ziploc, a la cual le pueden cortar una punta. y comienzan cuidadosamente a formar un disco sobre la bandeja forrada con el papel de mantequilla, como se aprecia en la foto de arriba., 4-llevar al horno por 1 hora y media , es muy importante que el horno no supere los 100°c (200°)., 5-cuando los discos estén secos es porque ya están listos. y una vez fríos, comenzamos a rellenar., 6-con unos 100 grs gramos de las frutillas las molemos y las pasamos por cedazo. reservar., 7-en un bol batimos la crema y vamos agregando el azúcar flor, luego agregamos el puré de frutillas. mezclamos bien., 8-y encima de un disco de merengue colocamos un capa de crema, luego unos trozos de frutilla, luego otra capa delgada de crema. enseguida ponemos otro disco de merengue y realizamos el mismo paso que el anterior hasta finalizar, decoramos por fuera de la torta con la crema y unas frutillas del modo deseado.</t>
         </is>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>10</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J65" t="n">
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K65" t="n">
         <v>39.88413547237077</v>
       </c>
     </row>
@@ -2999,39 +3196,42 @@
       <c r="A66" t="n">
         <v>64</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" t="n">
+        <v>109</v>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>Torta ideal de piña para el día de la madre</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>35</v>
       </c>
-      <c r="D66" t="n">
+      <c r="E66" t="n">
         <v>20</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>24</v>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>6 huevos, 2 tazas (280 grs.) de azúcar flor cernida, 2 tazas de harina (280 grs.) cernida, 2 cucharaditas de polvos de hornear, 6 cucharadas de agua, 1pizca de sal, 1 tarro de leche evaporada refrigerado por varias horas, 4 cucharadas de jugo de limón, 4 cucharadas de azúcar granulada, 2 1/2 cucharaditas rasas (14 grs) de gelatina sin sabor, 425 grs de piña picada y escurrida (reservar el jugo de la piña), 500 grs de mermelada de damasco pasada por cedazo, 400 ml de crema para batir, 120 grs de azúcar flor</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>1-batir las yemas con el azúcar flor hasta que estén casi blancas, añadirles el agua y luego la harina cernida con los polvos de hornear y la pizca de sal. incorporar suavemente las claras batidas a nieve., 2-vertir en un molde (26 cm) previamente enmantequillado y llevar al horno a 350° f (180° c) por unos 35 minutos apróximadamente., 3-desmoldar y dejar enfríar., 4-preparación relleno y decorado:, 5-batir la leche evaporada al doble de su volumen. siempre batiendo añadir de a poco el jugo de limón, luego el azúcar granulada y la gelatina disuelta en un poquito de agua caliente. batir unos 2 a 3 minutos más., 6-dividir el bizcocho en 2 partes ( o en tres). con el jugo de la piña más un poco de azúcar y agua, agregar al bizcocho para remojarlo, luego pintar ambas caras del bizcocho con la mermelada y rellenar con una capa de crema ideal y encima con piña picada. hacer lo mismo si se logra dividir en 3 partes y eso va a depender de que tan alto logren hacer el bizcocho., 7-finalmente tapice y decore la torta con crema batida con azúcar flor y algunos trozos de piña. mantener en el refrigerador hasta el momento de servir., 8-batir la leche evaporada al doble de su volumen. siempre batiendo añadir de a poco el jugo de limón, luego el azúcar granulada y la gelatina disuelta en un poquito de agua caliente. batir unos 2 a 3 minutos más., 9-dividir el bizcocho en 2 partes ( o en tres). con el jugo de la piña más un poco de azúcar y agua, agregar al bizcocho para remojarlo, luego pintar ambas caras del bizcocho con la mermelada y rellenar con una capa de crema ideal y encima con piña picada. hacer lo mismo si se logra dividir en 3 partes y eso va a depender de que tan alto logren hacer el bizcocho., 10-finalmente tapice y decore la torta con crema batida con azúcar flor y algunos trozos de piña. mantener en el refrigerador hasta el momento de servir.</t>
         </is>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>14</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J66" t="n">
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K66" t="n">
         <v>48.97504456327985</v>
       </c>
     </row>
@@ -3039,39 +3239,42 @@
       <c r="A67" t="n">
         <v>65</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" t="n">
+        <v>111</v>
+      </c>
+      <c r="C67" t="inlineStr">
         <is>
           <t>Tortilla de porotos verdes</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>35</v>
       </c>
-      <c r="D67" t="n">
-        <v>6</v>
-      </c>
       <c r="E67" t="n">
         <v>6</v>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="n">
+        <v>6</v>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>1/2 kilo de porotos verdes, 5 huevos medianos, sal a gusto, 1 cucharadita de aceite</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>1-cocinar los porotos verdes en agua caliente por unos 5 minutos desde que empieza hervir el agua., 2-luego pasarlos por agua fría para enfríar., 3-enseguida ir cortando a lo largo los porotos o también puede ser diagonalmente., 4-en un bowl batir los huevos, agregar la sal y los porotos. mezclar bien., 5-vertir la mezcla en una sartén antiadherente previamente calentado y con una cucharadita de aceite., 6-cocinar a fuego medio 5 minutos por lado. debe ir despegando los bordes con la ayuda de una espátula., 7-ayudarse con un plato para dar vuelta la tortilla.</t>
         </is>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>4</v>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J67" t="n">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K67" t="n">
         <v>26.24777183600713</v>
       </c>
     </row>
@@ -3079,39 +3282,42 @@
       <c r="A68" t="n">
         <v>66</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" t="n">
+        <v>113</v>
+      </c>
+      <c r="C68" t="inlineStr">
         <is>
           <t>Tortilla de zapallo italiano</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>25</v>
-      </c>
-      <c r="D68" t="n">
-        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>2 zapallos italianos, 1/2 unidad de cebolla picada fina, 1 diente de ajo picado fino, 1/2 cucharada de aceite de oliva, sal y pimienta a gusto, 3 huevos, aceite en spray</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>1-lavar los zapallos italianos, cortar los extremos y rallarlos con cáscaras., 2-luego con la ayuda de un paño o simplemente con la mano extraer el exceso de líquido un poco. reservar., 3-luego en un sartén freír la cebolla y el ajo con el aceite de oliva por unos 3 minutos a fuego medio., 4-mientras tanto en un bol batir los huevos y agregar la mezcla de cebolla y ajo. sazonar con sal y pimienta. luego agregar el zapallo italiano rallado., 5-en un sartén antidherente rociar con aceite en spray o esparcir un poco de otro tipo., 6-colocar la mezcla de zapallo italiano y cocinar a fuego medio fuerte por 1 minuto aproximadamente. luego bajar a fuego medio bajo. dejar por unos 6 minutos o hasta que se desprenda la tortilla. luego, con la ayuda de un plato o algo similar, dar vuelta la tortilla y cocinar por otros 6 minutos o hasta que esté dorada.</t>
         </is>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>7</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">duracion Media </t>
-        </is>
-      </c>
-      <c r="J68" t="n">
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">duracion Media </t>
+        </is>
+      </c>
+      <c r="K68" t="n">
         <v>28.16399286987522</v>
       </c>
     </row>
@@ -3119,39 +3325,42 @@
       <c r="A69" t="n">
         <v>67</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" t="n">
+        <v>115</v>
+      </c>
+      <c r="C69" t="inlineStr">
         <is>
           <t>Vaina, cocktail chileno</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>10</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>50 cc de vino añejo u oporto, 30 cc de cognac, 30 cc de licor de cacao, 1 o 2 cucharaditas de azúcar flor, 1 yema de huevo, canela en polvo, ½ taza de hielo</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>1-mezclar todos los ingredientes menos la canela, en una coctelera, también puede usar una licuadora., 2-servir en una copa flauta fría, con canela en polvo encima.</t>
         </is>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>7</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>duracion Rapida</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>20.81105169340464</v>
       </c>
     </row>
